--- a/workspaces/btc_daily_14days/volatility/bb_pct_20.xlsx
+++ b/workspaces/btc_daily_14days/volatility/bb_pct_20.xlsx
@@ -575,46 +575,46 @@
         <v>36</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.062117235344317</v>
+        <v>3.052062981952872</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.662944543380014</v>
+        <v>-9.632042832932179</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.722942827425328</v>
+        <v>-1.717483052100974</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.186824855246279</v>
+        <v>1.182938692213774</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.428849407811661</v>
+        <v>3.417263818493964</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-12.95981863225504</v>
+        <v>-12.91853449480966</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.920236935468409</v>
+        <v>-1.914442810649561</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.176516384499664</v>
+        <v>3.165917759841577</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3327429005987028</v>
+        <v>0.3315873114276044</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.303194709411471</v>
+        <v>-3.292616298269344</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.078704587683198</v>
+        <v>-9.049422719739134</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.261211691153513</v>
+        <v>-6.240893220136648</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-12.25644385974333</v>
+        <v>-12.2167780923816</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.222004233925773</v>
+        <v>-9.192330195203638</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.1124440306782972</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-13.63223459650035</v>
+        <v>-13.58786378278574</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.266404030380542</v>
+        <v>-9.236382943805381</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.755607606561973</v>
+        <v>-6.733820826630307</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-12.06272466991822</v>
+        <v>-12.02431355423697</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-7.000315737142948</v>
+        <v>-6.97754865079925</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-11.85579003742655</v>
+        <v>-11.8176731864087</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.941510000630892</v>
+        <v>-9.909787515491587</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-12.39104007100523</v>
+        <v>-12.35096896624416</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.701055513079268</v>
+        <v>-3.688981514276513</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-8.68132635538197</v>
+        <v>-8.65276317355373</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.261547029763015</v>
+        <v>-6.240832249483169</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.684927641003853</v>
+        <v>-6.662552592091501</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.435770980516324</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>78</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.347914456389638</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.435290267428968</v>
+        <v>7.411361659583278</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13.45563522222204</v>
+        <v>13.4114487859342</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.325190378128227</v>
+        <v>3.314312875198944</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2204725279538522</v>
+        <v>0.2194451315057435</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.936553308575533</v>
+        <v>6.913937066527581</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.00150926077297</v>
+        <v>2.99166810854814</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.103067041774025</v>
+        <v>5.086017196461924</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.188950600218</v>
+        <v>1.18534638805221</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3372367052625549</v>
+        <v>0.3363277643439488</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.580295626296689</v>
+        <v>-7.55450096370933</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-6.2620834610087</v>
+        <v>-6.240734716528642</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.827632116482306</v>
+        <v>-2.817327219136743</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.150116626485122</v>
+        <v>-5.132501135373325</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>91</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>12.3417265149546</v>
+        <v>12.29952150798525</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.038622191488372</v>
+        <v>3.028521428020426</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.843391339385484</v>
+        <v>4.826409189154681</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.373981255524761</v>
+        <v>9.342152807684933</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.937565480532854</v>
+        <v>9.903605035821073</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.0372699865245</v>
+        <v>8.009933238952598</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.552019605053779</v>
+        <v>3.539882230698211</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.08514141518193</v>
+        <v>3.074171134901242</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.024372821157527</v>
+        <v>3.014397976155649</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.131378243002963</v>
+        <v>-1.12735659727403</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.541349275365093</v>
+        <v>-3.5280896308943</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.405680314111017</v>
+        <v>-2.396444379600297</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.725706925337569</v>
+        <v>-1.718678127921315</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.475450991270534</v>
+        <v>-1.469497472369653</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>100</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4934383202099752</v>
+        <v>-0.4931958568430446</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.895499151941699</v>
+        <v>1.888855045435498</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4999912707920657</v>
+        <v>-0.4992721691547786</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.6310813793036871</v>
+        <v>0.6280095379471007</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.099900021839346</v>
+        <v>7.074066603597153</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.619144742287261</v>
+        <v>-6.596946052092306</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.701085515746868</v>
+        <v>-3.688637985512763</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.175514538563398</v>
+        <v>-7.15138906801139</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-11.24759212780659</v>
+        <v>-11.20848107359975</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-13.10538208404257</v>
+        <v>-13.05954536633597</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.293807242460886</v>
+        <v>-5.273780812193358</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.257678761180699</v>
+        <v>-4.24153557104237</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.690225504180027</v>
+        <v>-7.662111103494219</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.438054980423203</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>129</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.33064762253538</v>
+        <v>-1.327376575270527</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.718425788935726</v>
+        <v>-3.705285974112577</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.314960160093442</v>
+        <v>1.309192635394155</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.209272642585816</v>
+        <v>-3.198717365832536</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.972766202553402</v>
+        <v>-2.963984779118235</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3474383913940571</v>
+        <v>-0.346404895691478</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4324542368205186</v>
+        <v>-0.4309817127335336</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.007407702529783</v>
+        <v>-3.993155060358198</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.739687480220155</v>
+        <v>-1.732316827177748</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.147088129755836</v>
+        <v>-4.130587296061492</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.576852143271083</v>
+        <v>-3.561735559004958</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.320752366716988</v>
+        <v>-4.303358692798376</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.299654101895591</v>
+        <v>-6.274762079524344</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-6.828547363564851</v>
+        <v>-6.802149316649405</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.280755228177121</v>
+        <v>4.294764340996281</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7338918672570856</v>
+        <v>0.735904948101151</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.275829012173574</v>
+        <v>2.283690107564688</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.406803755304551</v>
+        <v>2.414538883848735</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.868822946698245</v>
+        <v>1.875766061166651</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.16679304557627</v>
+        <v>2.173442957120656</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.795215374996815</v>
+        <v>-1.80057445011704</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.264073032052316</v>
+        <v>-2.271146850118065</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.326564510095693</v>
+        <v>-2.334687601067444</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5928870814324654</v>
+        <v>-0.5964694743563541</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.142019316208128</v>
+        <v>1.143125574284895</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.176902143056509</v>
+        <v>1.178378890184405</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.696929178026885</v>
+        <v>2.702428992001735</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.375832026569057</v>
+        <v>1.377655374783195</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>138</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3205347614582834</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.417445704689221</v>
+        <v>2.408823615542893</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.298281692724984</v>
+        <v>1.291916393401642</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.879611928046288</v>
+        <v>2.868161433585477</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.011259660452644</v>
+        <v>-2.005974671888133</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.988682702074918</v>
+        <v>-0.9856483260298745</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.074223111764724</v>
+        <v>-1.070081080225627</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8168419710069088</v>
+        <v>-0.8131662726242226</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.752914365351877</v>
+        <v>2.744778876320296</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.17413585997874</v>
+        <v>1.172258499754562</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.66552490445472</v>
+        <v>-2.653151687474001</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.631748831251151</v>
+        <v>-2.619838178568784</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.054955503766521</v>
+        <v>-3.041085343903781</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.6223794087300121</v>
+        <v>-0.6174509681492353</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.212444032731064</v>
+        <v>2.219228081877986</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.308459630157053</v>
+        <v>5.32137720812937</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.915345991132064</v>
+        <v>4.928445997349662</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.280956283944633</v>
+        <v>3.289848657777391</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.921082245303666</v>
+        <v>3.931680455119782</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.041463142024014</v>
+        <v>3.049047994989131</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.725200654099737</v>
+        <v>4.736270752287098</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1313476287018958</v>
+        <v>0.1310815385543265</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.60813243827365</v>
+        <v>3.615820451709929</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.373502159157411</v>
+        <v>-1.378325141446965</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.990284258269476</v>
+        <v>-0.994824790933059</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.726925828405115</v>
+        <v>-2.735400978012407</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.39940497324114</v>
+        <v>-3.409835879878266</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.379734220160302</v>
+        <v>-1.384966618608033</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.278778634346097</v>
+        <v>-3.283470315784925</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-5.415622741554621</v>
+        <v>-5.425056312563228</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-8.955636617331102</v>
+        <v>-8.970789035576907</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-9.352306975523781</v>
+        <v>-9.368592305025267</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.700114263694047</v>
+        <v>-5.709387998212684</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.880154379665726</v>
+        <v>-4.888723148060159</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.540805629678999</v>
+        <v>-6.552760547097982</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.288946441578886</v>
+        <v>-2.293677170972764</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.925880602987661</v>
+        <v>-3.933642242528137</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.831869395615449</v>
+        <v>-5.844127029483268</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.939082057213419</v>
+        <v>-3.948293813681552</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.129210386561461</v>
+        <v>-4.138755980861134</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.921657087457262</v>
+        <v>-1.927431644437853</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.875574308767973</v>
+        <v>-5.888236627950917</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-7.443933369714813</v>
+        <v>-7.492305871835015</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-8.068324659576781</v>
+        <v>-8.125141718414106</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-11.43865326680122</v>
+        <v>-11.5173481590291</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-9.825808020972339</v>
+        <v>-9.894870850373813</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.906130971494186</v>
+        <v>-5.945009347166604</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.859217210006157</v>
+        <v>-2.879510254778751</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.447922799147406</v>
+        <v>-2.467234979188355</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.410576384574945</v>
+        <v>-3.437594169511677</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.479973354741716</v>
+        <v>-2.501073835772125</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.838609796207976</v>
+        <v>-1.859847683211413</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2293067424162629</v>
+        <v>0.2215977038985741</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.242396002138811</v>
+        <v>3.255980861244012</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.314946606017863</v>
+        <v>4.335726250299111</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.087328416555913</v>
+        <v>1.085447582575284</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>174</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.516426825957105</v>
+        <v>-6.496542198406097</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.256689708756745</v>
+        <v>-5.23866980294882</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.353448738429215</v>
+        <v>-3.341475194370886</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.378332102586384</v>
+        <v>1.376110308005174</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3108251866294509</v>
+        <v>-0.3098699589910936</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.864751323452232</v>
+        <v>2.85656384314003</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.204541872627132</v>
+        <v>2.199212832177132</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.312506116885416</v>
+        <v>2.307485250694967</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.099332595589573</v>
+        <v>1.098169964862947</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.397650496202964</v>
+        <v>1.397615396032251</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.380708239834895</v>
+        <v>6.365275864818116</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.380391134502219</v>
+        <v>2.376670516416297</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.535391269870686</v>
+        <v>2.531128549149685</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6737674114685603</v>
+        <v>-0.667425980642868</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.334782538685587</v>
+        <v>3.405191121380234</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.958975705148404</v>
+        <v>-2.027253660253507</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.667798608970145</v>
+        <v>1.688829092089009</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.024897673702704</v>
+        <v>3.081487541678172</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.088609060052839</v>
+        <v>-2.138040325605125</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.794276832859275</v>
+        <v>-1.837410445655692</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.378241584236207</v>
+        <v>-3.466152248224063</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.520819130610555</v>
+        <v>-7.710947123852584</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.738665627015067</v>
+        <v>-5.889701963467296</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.908317548516948</v>
+        <v>-1.985598657318434</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.188308074505393</v>
+        <v>-5.335006069686322</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.768437993662801</v>
+        <v>-5.929553729950953</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-6.17978654075371</v>
+        <v>-6.349808340895855</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.696586023544668</v>
+        <v>-4.842225373399444</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.855854427592526</v>
+        <v>-6.944681897189028</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.100171640216445</v>
+        <v>-3.154166714568596</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.837895573467023</v>
+        <v>-4.908435817373046</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.366278808009653</v>
+        <v>-3.414797912934112</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.233186156396592</v>
+        <v>-3.276324456194743</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-4.950687149989072</v>
+        <v>-5.015758501805998</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-8.394559041037539</v>
+        <v>-8.509170543531681</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.797543305316182</v>
+        <v>-5.885594585801236</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-9.509999738439276</v>
+        <v>-9.645292494238753</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.34349178554288</v>
+        <v>-10.49541767926683</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-10.54720553873965</v>
+        <v>-10.70017100358441</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-10.51230259583426</v>
+        <v>-10.66578784623898</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.225229928690432</v>
+        <v>-6.32413769527912</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.645682014374529</v>
+        <v>-6.754688471846372</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.450272852583915</v>
+        <v>-6.497963416536557</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.588440915721868</v>
+        <v>-1.608860273437564</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-6.301903623895065</v>
+        <v>-6.351874431328142</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.775036602645777</v>
+        <v>-5.818902869482493</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.432925668431672</v>
+        <v>-3.458773359916655</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.416908132888793</v>
+        <v>-2.436693741041402</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-7.53463758636908</v>
+        <v>-7.593891226429953</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-6.556660100667806</v>
+        <v>-6.611799262892617</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.055107837646212</v>
+        <v>-8.122074511393592</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.016691184559384</v>
+        <v>-6.07364897178384</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.781326761805232</v>
+        <v>-4.829126933782582</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.625695822895111</v>
+        <v>-7.693294501074831</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.20434712359729</v>
+        <v>-10.28746215549815</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.794152515571099</v>
+        <v>-7.863827779743445</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.548232840757763</v>
+        <v>-4.586837889782132</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.038383854198003</v>
+        <v>-3.070529174553542</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.115933119030018</v>
+        <v>-4.155053053563925</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-8.784059303420229</v>
+        <v>-8.852386127852817</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.582432927007353</v>
+        <v>-6.632186653269819</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-6.971530316579781</v>
+        <v>-7.024399887968109</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.308498904261548</v>
+        <v>-4.350512915585057</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.085284206702617</v>
+        <v>-4.128041141952764</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.7187324818490524</v>
+        <v>-0.7407651660664172</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.559853872420526</v>
+        <v>-1.590890351094188</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9751188306591558</v>
+        <v>0.962977014243414</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.413547725803369</v>
+        <v>-2.45091569048013</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5927845820247057</v>
+        <v>0.5771055606440996</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.267485012635042</v>
+        <v>4.275102754989035</v>
       </c>
     </row>
     <row r="22">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.08461</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4075~4088</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4075</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.07171620670704471</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.04246</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4039~4052</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4039</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.09955875456338248</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.0003109</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3997~4010</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3997</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.09942335761645893</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.04184</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3919~3932</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3919</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.1282297749403938</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.08399</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3828~3841</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3828</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.4236648237246783</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.1261</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3728~3741</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3728</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.4217997209049713</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.1683</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3599~3612</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3599</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.3893408672753154</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.2104</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3445~3457</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3445</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.5987319273838239</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.2526</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3307~3319</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3307</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.6103410017405579</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.2947</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3138~3149</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3138</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.7627301588889139</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.3369</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2948~2958</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2948</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.6002672586819102</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.379</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2748~2756</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2748</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.09866328392550372</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.4212</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2574~2582</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2574</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.333827365305126</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.4633</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2415~2419</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2415</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.1316133540355864</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.5055</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2268~2270</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2268</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.5902621203186627</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.5476</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2130~2131</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2130</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.049499267776888</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.5898</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1985~1985</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1985</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.461221629412186</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.632</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1834~1834</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1834</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.977663097456329</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.6741</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1681~1681</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1681</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.176401061110667</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.7163</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1513~1513</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1513</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.901802922354463</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.7584</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1306~1306</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1306</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.71789399219432</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.8006</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1108~1108</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1108</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>2.831471427082441</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.8427</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>923~923</t>
-        </is>
+      <c r="B28" t="n">
+        <v>923</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>2.652823868305731</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.8849</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>744~744</t>
-        </is>
+      <c r="B29" t="n">
+        <v>744</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.151722970112601</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.927</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>558~558</t>
-        </is>
+      <c r="B30" t="n">
+        <v>558</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.52448282674343</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.9692</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>405~405</t>
-        </is>
+      <c r="B31" t="n">
+        <v>405</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.827549334111012</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 1.011</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>297~297</t>
-        </is>
+      <c r="B32" t="n">
+        <v>297</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.735517908746253</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 1.053</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>210~210</t>
-        </is>
+      <c r="B33" t="n">
+        <v>210</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>2.268466441694791</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 1.096</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>129~129</t>
-        </is>
+      <c r="B34" t="n">
+        <v>129</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-2.881035219434779</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 1.138</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>3.458942632170981</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.08461</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>4.649418822647164</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.04246</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>120~120</t>
-        </is>
+      <c r="B7" t="n">
+        <v>120</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>4.173228346456689</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.0003109</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>162~162</t>
-        </is>
+      <c r="B8" t="n">
+        <v>162</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3.062117235345582</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.04184</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>240~240</t>
-        </is>
+      <c r="B9" t="n">
+        <v>240</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>2.506561679790032</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.08399</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>331~331</t>
-        </is>
+      <c r="B10" t="n">
+        <v>331</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>5.210489172237153</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.1261</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>431~431</t>
-        </is>
+      <c r="B11" t="n">
+        <v>431</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.887072120625291</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.1683</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>560~560</t>
-        </is>
+      <c r="B12" t="n">
+        <v>560</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>2.685133108361455</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.2104</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>714~715</t>
-        </is>
+      <c r="B13" t="n">
+        <v>714</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>3.031037204265552</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.2526</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>852~853</t>
-        </is>
+      <c r="B14" t="n">
+        <v>852</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.488976685651686</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.2947</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1021~1023</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1021</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.44302306786431</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.3369</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1211~1214</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1211</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.542805501865807</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.379</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1411~1416</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1411</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.2607989679256235</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.4212</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1585~1590</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1585</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.4808597038577744</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.4633</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1744~1753</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1744</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.1260680977342261</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.5055</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1891~1902</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1891</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.6532700762562413</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.5476</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2029~2041</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2029</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.048068403502484</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.5898</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2174~2187</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2174</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.281732787516788</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.632</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2325~2338</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2325</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.509691528079948</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.6741</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2478~2491</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2478</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.429608532975934</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.7163</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2646~2659</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2646</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.04552557105616</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.7584</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2853~2866</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2853</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.7488465546831051</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.8006</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3051~3064</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3051</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.9921328371812521</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.8427</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3236~3249</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3236</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.7236630047282802</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.8849</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3415~3428</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3415</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.6556320191598033</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.927</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3601~3614</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3601</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.3628351104700727</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.9692</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3754~3767</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3754</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.1706350284658811</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 1.011</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3862~3875</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3862</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.2611802556938514</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 1.053</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3949~3962</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3949</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.09565942066429045</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 1.096</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4030~4043</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4030</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1160101091741481</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 1.138</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4075~4088</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4075</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.04725436717671272</v>

--- a/workspaces/btc_daily_14days/volatility/bb_pct_20.xlsx
+++ b/workspaces/btc_daily_14days/volatility/bb_pct_20.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that BB Pct-20 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that BB Pct-20 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,254 +575,254 @@
         <v>36</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.052062981952872</v>
+        <v>3.064546631583141</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.632042832932179</v>
+        <v>-9.619179236161322</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.717483052100974</v>
+        <v>-1.704513256433749</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.182938692213774</v>
+        <v>1.19588573239249</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.417263818493964</v>
+        <v>3.430346825872434</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-12.91853449480966</v>
+        <v>-12.90552425671926</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.914442810649561</v>
+        <v>-1.901400449388809</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.165917759841577</v>
+        <v>3.179079984342295</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3315873114276044</v>
+        <v>0.3447694419202421</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.292616298269344</v>
+        <v>-3.279225568043955</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.049422719739134</v>
+        <v>-9.035977343946428</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.240893220136648</v>
+        <v>-6.227448537875688</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-12.2167780923816</v>
+        <v>-12.20322624696959</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.192330195203638</v>
+        <v>-9.202759830899268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02139</t>
+          <t>X ≈ -0.02138</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1124440306782972</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-13.58786378278574</v>
+        <v>-13.57500418541714</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.236382943805381</v>
+        <v>-9.223419058544685</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.733820826630307</v>
+        <v>-6.720879338443943</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-12.02431355423697</v>
+        <v>-12.01123972610971</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-6.97754865079925</v>
+        <v>-6.964536204078918</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-11.8176731864087</v>
+        <v>-11.80463563618545</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.909787515491587</v>
+        <v>-9.896630535254253</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-12.35096896624416</v>
+        <v>-12.33779112050594</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.688981514276513</v>
+        <v>-3.675591179648123</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-8.65276317355373</v>
+        <v>-8.639317988653495</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.240832249483169</v>
+        <v>-6.2273877307885</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.662552592091501</v>
+        <v>-6.649000496021863</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.02076</t>
+          <t>X ≈ 0.02077</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>78</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.347914456389638</v>
+        <v>1.360394790181495</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.411361659583278</v>
+        <v>7.424235758513333</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13.4114487859342</v>
+        <v>13.42442732432097</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.314312875198944</v>
+        <v>3.327259607117064</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2194451315057435</v>
+        <v>0.2325247795433967</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.913937066527581</v>
+        <v>6.926955693048519</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.99166810854814</v>
+        <v>3.004711357538106</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.086017196461924</v>
+        <v>5.099179175888793</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.18534638805221</v>
+        <v>1.198527874813635</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3363277643439488</v>
+        <v>0.3497186646166597</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.55450096370933</v>
+        <v>-7.541055986344887</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-6.240734716528642</v>
+        <v>-6.22729046043834</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.817327219136743</v>
+        <v>-2.803775007166998</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.132501135373325</v>
+        <v>-5.142930771072052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.06291</t>
+          <t>X ≈ 0.06293</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>91</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>12.29952150798525</v>
+        <v>12.31200973178048</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.028521428020426</v>
+        <v>3.041390632585866</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.826409189154681</v>
+        <v>4.839380474616128</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.342152807684933</v>
+        <v>9.355102310830411</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.903605035821073</v>
+        <v>9.91668925248414</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.009933238952598</v>
+        <v>8.022951553597565</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.539882230698211</v>
+        <v>3.552924788480027</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.074171134901242</v>
+        <v>3.087331544054031</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.014397976155649</v>
+        <v>3.027579341533844</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.12735659727403</v>
+        <v>-1.113966720097316</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.5280896308943</v>
+        <v>-3.514644441829468</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.396444379600297</v>
+        <v>-2.382999991431788</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.718678127921315</v>
+        <v>-1.705126019347951</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.469497472369653</v>
+        <v>-1.479927108067308</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.105</t>
+          <t>X ≈ 0.1051</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>100</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4931958568430446</v>
+        <v>-0.480720715371632</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.888855045435498</v>
+        <v>1.901721323959173</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4992721691547786</v>
+        <v>-0.4863067191381205</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.6280095379471007</v>
+        <v>0.6409516108799238</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.074066603597153</v>
+        <v>7.087147956520248</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.596946052092306</v>
+        <v>-6.583937150998679</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.688637985512763</v>
+        <v>-3.675600182564196</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.15138906801139</v>
+        <v>-7.138234049129331</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-11.20848107359975</v>
+        <v>-11.19530565292999</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-13.05954536633597</v>
+        <v>-13.04615971605969</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.273780812193358</v>
+        <v>-5.260336661058112</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.24153557104237</v>
+        <v>-4.228091872142279</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.662111103494219</v>
+        <v>-7.648559631403927</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053123209</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>129</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.327376575270527</v>
+        <v>-1.314905260403322</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.705285974112577</v>
+        <v>-3.692427511394889</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.309192635394155</v>
+        <v>1.322156962078324</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.198717365832536</v>
+        <v>-3.185780548109598</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.963984779118235</v>
+        <v>-2.950911935061661</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.346404895691478</v>
+        <v>-0.333394542315034</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4309817127335336</v>
+        <v>-0.4179440777205201</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.993155060358198</v>
+        <v>-3.980000428364903</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.732316827177748</v>
+        <v>-1.719139501388106</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.130587296061492</v>
+        <v>-4.117200378829608</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.561735559004958</v>
+        <v>-3.548291928715777</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.303358692798376</v>
+        <v>-4.289915593412864</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.274762079524344</v>
+        <v>-6.261210829492462</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-6.802149316649405</v>
+        <v>-6.812578952347913</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.294764340996281</v>
+        <v>4.275666550262436</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.735904948101151</v>
+        <v>0.7442266949592877</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.283690107564688</v>
+        <v>2.278936148899824</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.414538883848735</v>
+        <v>2.410044841904039</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.875766061166651</v>
+        <v>1.873192282443128</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.173442957120656</v>
+        <v>2.171466059807265</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.80057445011704</v>
+        <v>-1.775462773508693</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.271146850118065</v>
+        <v>-2.242052108728551</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.334687601067444</v>
+        <v>-2.303206149642108</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5964694743563541</v>
+        <v>-0.5750097027006262</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.143125574284895</v>
+        <v>1.154076119953906</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.178378890184405</v>
+        <v>1.188494093326874</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.702428992001735</v>
+        <v>2.70358617277261</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.377655374783195</v>
+        <v>1.639534075909793</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>138</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3205347614582834</v>
+        <v>-0.308155029025734</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.408823615542893</v>
+        <v>2.420960894861302</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.291916393401642</v>
+        <v>1.304343004878504</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.868161433585477</v>
+        <v>2.880142053632461</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.005974671888133</v>
+        <v>-1.992467361442898</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9856483260298745</v>
+        <v>-0.9723912377638584</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.070081080225627</v>
+        <v>-1.056703897039</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8131662726242226</v>
+        <v>-0.7997085634138443</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.744778876320296</v>
+        <v>2.757276296454322</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.172258499754562</v>
+        <v>1.185487499205159</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.653151687474001</v>
+        <v>-2.638679219181022</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.619838178568784</v>
+        <v>-2.605403913617785</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.041085343903781</v>
+        <v>-3.026378839671217</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.6174509681492353</v>
+        <v>-0.6278806038473874</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>169</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.219228081877986</v>
+        <v>2.23088468033955</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.32137720812937</v>
+        <v>5.332615187954552</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.928445997349662</v>
+        <v>4.939761721839965</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.289848657777391</v>
+        <v>3.30169868978966</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.931680455119782</v>
+        <v>3.943441294651144</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.049047994989131</v>
+        <v>3.061145451653211</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.736270752287098</v>
+        <v>4.747934536789366</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1310815385543265</v>
+        <v>0.1443700526774236</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.615820451709929</v>
+        <v>3.628076510631573</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.378325141446965</v>
+        <v>-1.364194685497992</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.994824790933059</v>
+        <v>-0.9806732245458392</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.735400978012407</v>
+        <v>-2.720726081283082</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.409835879878266</v>
+        <v>-3.737035255204717</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.384966618608033</v>
+        <v>-1.395396254306185</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>190</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.283470315784925</v>
+        <v>-3.270071074277638</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-5.425056312563228</v>
+        <v>-5.410401201497884</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-8.970789035576907</v>
+        <v>-8.954991184523216</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-9.368592305025267</v>
+        <v>-9.352609735960982</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.709387998212684</v>
+        <v>-5.694541410248213</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.888723148060159</v>
+        <v>-4.874066105273116</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.552760547097982</v>
+        <v>-6.537457371557849</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.293677170972764</v>
+        <v>-2.279566371285064</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.933642242528137</v>
+        <v>-3.918955505732725</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.844127029483268</v>
+        <v>-5.828406565537833</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.948293813681552</v>
+        <v>-3.933068437700499</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.138755980861134</v>
+        <v>-4.426438817306462</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.927431644437853</v>
+        <v>-1.91387559808625</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.888236627950917</v>
+        <v>-5.898666263649069</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>200</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-7.492305871835015</v>
+        <v>-7.738284880384093</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-8.125141718414106</v>
+        <v>-8.109165392527245</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-11.5173481590291</v>
+        <v>-11.50013497473102</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-9.894870850373813</v>
+        <v>-9.878175423942146</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.945009347166604</v>
+        <v>-5.92973582790848</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.879510254778751</v>
+        <v>-3.139024717845643</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.467234979188355</v>
+        <v>-2.453102986889618</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.437594169511677</v>
+        <v>-3.422940370982815</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.501073835772125</v>
+        <v>-2.486701253093685</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.859847683211413</v>
+        <v>-1.845251890200274</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2215977038985741</v>
+        <v>-0.05283920381555873</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.255980861244012</v>
+        <v>3.269433149964122</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.335726250299111</v>
+        <v>4.349282296650713</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.085447582575284</v>
+        <v>1.075017946877132</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>174</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.496542198406097</v>
+        <v>-6.484019908730474</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.23866980294882</v>
+        <v>-5.223575939292409</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.341475194370886</v>
+        <v>-3.327029583989116</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.376110308005174</v>
+        <v>1.388765901805989</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3098699589910936</v>
+        <v>-0.2966786485853703</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.85656384314003</v>
+        <v>2.869606739434396</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.199212832177132</v>
+        <v>2.211582879279277</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.307485250694967</v>
+        <v>2.320015746300285</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.098169964862947</v>
+        <v>1.111207692322353</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.397615396032251</v>
+        <v>1.411008020533558</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.365275864818116</v>
+        <v>6.378733158528334</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.376670516416297</v>
+        <v>2.390122805136407</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.531128549149685</v>
+        <v>2.544684595501288</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.667425980642868</v>
+        <v>-0.6778556163410201</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>159</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.405191121380234</v>
+        <v>3.417713411055857</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.027253660253507</v>
+        <v>-2.012612305993095</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.688829092089009</v>
+        <v>1.355160657522312</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.081487541678172</v>
+        <v>3.093820928901081</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.138040325605125</v>
+        <v>-2.469708212210698</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.837410445655692</v>
+        <v>-1.824367549361327</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.466152248224063</v>
+        <v>-3.798863296586653</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.710947123852584</v>
+        <v>-7.694216647987986</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.889701963467296</v>
+        <v>-5.873648700499707</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.985598657318434</v>
+        <v>-2.333431851702613</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.335006069686322</v>
+        <v>-5.321548775976105</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.929553729950953</v>
+        <v>-5.916101441230843</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-6.349808340895855</v>
+        <v>-6.336252294544252</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.842225373399444</v>
+        <v>-4.852655009097596</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>147</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.944681897189028</v>
+        <v>-6.932159607513405</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.154166714568596</v>
+        <v>-3.139071638850162</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.908435817373046</v>
+        <v>-4.895428685955444</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.414797912934112</v>
+        <v>-3.399816961097265</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.276324456194743</v>
+        <v>-3.263213651819804</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.015758501805998</v>
+        <v>-5.002715605511632</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-8.509170543531681</v>
+        <v>-8.496104289231205</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.885594585801236</v>
+        <v>-6.255031339599363</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-9.645292494238753</v>
+        <v>-10.01530995567168</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.49541767926683</v>
+        <v>-10.482012551614</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-10.70017100358441</v>
+        <v>-10.68671370987419</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-10.66578784623898</v>
+        <v>-10.65233555751887</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.32413769527912</v>
+        <v>-6.310581648927517</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.754688471846372</v>
+        <v>-6.765118107544524</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>138</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.497963416536557</v>
+        <v>-6.485441126860934</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.608860273437564</v>
+        <v>-1.594360582223295</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-6.351874431328142</v>
+        <v>-6.33886729991054</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.818902869482493</v>
+        <v>-6.204809784275767</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.458773359916655</v>
+        <v>-3.445662555541716</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.436693741041402</v>
+        <v>-2.423650844747037</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-7.593891226429953</v>
+        <v>-7.580824972129477</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-6.611799262892617</v>
+        <v>-6.59861825359738</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.122074511393592</v>
+        <v>-8.108875772438829</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.829126933782582</v>
+        <v>-4.815669640072365</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.693294501074831</v>
+        <v>-7.679842212354721</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.28746215549815</v>
+        <v>-10.27390610914655</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.863827779743445</v>
+        <v>-7.874257415441598</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>145</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.586837889782132</v>
+        <v>-4.574315600106509</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.070529174553542</v>
+        <v>-3.441767975796324</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.155053053563925</v>
+        <v>-4.142045922146323</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-8.852386127852817</v>
+        <v>-8.839406985454353</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.632186653269819</v>
+        <v>-6.61907584889488</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.024399887968109</v>
+        <v>-7.011356991673743</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.350512915585057</v>
+        <v>-4.337446661284581</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.128041141952764</v>
+        <v>-4.114860132657526</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.7407651660664172</v>
+        <v>-0.727566427111654</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.590890351094188</v>
+        <v>-1.577485223441357</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.962977014243414</v>
+        <v>0.9764343079536317</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.45091569048013</v>
+        <v>-2.43746340176002</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5771055606440996</v>
+        <v>0.5906616069957025</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.275102754989035</v>
+        <v>4.264673119290883</v>
       </c>
     </row>
     <row r="22">
@@ -1407,150 +1407,150 @@
         <v>151</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.811319114912109</v>
+        <v>-4.798796825236487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4626278272141136</v>
+        <v>-0.4497180176380624</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5.102768366851699</v>
+        <v>5.115775498269301</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.921763221313498</v>
+        <v>1.934742363711962</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.590167927533507</v>
+        <v>-2.577057123158568</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3059710229304287</v>
+        <v>-0.2929281266360633</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.039711362719267</v>
+        <v>-3.026645108418791</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1956364833550666</v>
+        <v>-0.1824554740598288</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.243391336424637</v>
+        <v>-2.230192597469873</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.106761554565296</v>
+        <v>-1.093356426912464</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.960521501399434</v>
+        <v>-3.947064207689216</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.926138344054003</v>
+        <v>-3.912686055333893</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.346392954998905</v>
+        <v>-4.332836908647302</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.758923278351759</v>
+        <v>-4.769352914049911</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.6531</t>
+          <t>X ≈ 0.653</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>153</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2058566208635639</v>
+        <v>-0.1933343311879412</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.471025005069649</v>
+        <v>-2.458115195493598</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.2515146266988495</v>
+        <v>-0.2385074952812474</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.735640579058739</v>
+        <v>-2.722661436660275</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.274061794131065</v>
+        <v>-3.260950989756125</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.59099894138258</v>
+        <v>-5.577956045088214</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.100569259962043</v>
+        <v>-1.087503005661567</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>0.4062126642771844</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.9751577736839394</v>
+        <v>-0.9619590347291762</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.17168818747011</v>
+        <v>-1.158283059817279</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.683631054271274</v>
+        <v>-2.670173760561056</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6884635832004307</v>
+        <v>-0.6750112944803206</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.415907736628917</v>
+        <v>-2.402351690277314</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.819781175594386</v>
+        <v>-2.830210811292538</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.6952</t>
+          <t>X ≈ 0.6951</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>168</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.823559495397198</v>
+        <v>4.836469304973249</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.238214598324348</v>
+        <v>3.25122172974195</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.535134397598583</v>
+        <v>7.548113539997047</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.210998896812121</v>
+        <v>5.224109701187061</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.103678929765877</v>
+        <v>6.116721826060243</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.399897593445985</v>
+        <v>8.412963847746461</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.7898570518073456</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.133619070386878</v>
+        <v>0.1468178093416412</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.7165061146409784</v>
+        <v>-0.7031009869881473</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.245407227708036</v>
+        <v>3.258864521418253</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.089314194577348</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.859535774108565</v>
+        <v>2.873091820460168</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.490209487337303</v>
+        <v>5.479779851639151</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>207</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.062117235345525</v>
+        <v>3.074639525021148</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.001268260062481374</v>
+        <v>0.01417806963853252</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3936004465341085</v>
+        <v>-0.3805933151165064</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.712622676245445</v>
+        <v>-1.699643533846981</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1644150458804532</v>
+        <v>0.1775258502553925</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.369060890800021</v>
+        <v>-4.356017994505656</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.970702820632688</v>
+        <v>-3.957636566332212</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-5.887161581733025</v>
+        <v>-5.873980572437787</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.015794318156871</v>
+        <v>-4.002595579202108</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4480901586509418</v>
+        <v>0.4614952863037729</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2053717957608114</v>
+        <v>-0.1919195070407014</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1425346192661081</v>
+        <v>-0.1289785729145052</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.791364011627493</v>
+        <v>-2.801793647325646</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>198</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-4.513640340411939</v>
+        <v>-4.501118050736316</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.955594127431823</v>
+        <v>1.968503937007874</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.97462811451836</v>
+        <v>-1.961620983100758</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-5.884779022314838</v>
+        <v>-5.871799879916374</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.897947712134417</v>
+        <v>-3.884836907759478</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.449999276086167</v>
+        <v>1.463042172380533</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.87031606386445</v>
+        <v>1.883382318164927</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.8980821600324447</v>
+        <v>0.9112631693276825</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.342132778900648</v>
+        <v>1.355331517855412</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.502108603973674</v>
+        <v>1.515513731626505</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2177962354954204</v>
+        <v>-0.2043389417852026</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.836788942052088</v>
+        <v>1.850241230772198</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.4064333210061832</v>
+        <v>0.4199893673577861</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>185</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.722777896006242</v>
+        <v>3.735300185681865</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.753660581822885</v>
+        <v>-2.740750772246834</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.716335576445452</v>
+        <v>1.729342707863054</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.089831952296137</v>
+        <v>5.102811094694601</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.470329656142823</v>
+        <v>3.483440460517762</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.605609431696443</v>
+        <v>1.618652327990809</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.683037876586205</v>
+        <v>3.696104130886681</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.317016753784635</v>
+        <v>5.330215492739399</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.547972649837838</v>
+        <v>5.561377777490669</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.883759866060863</v>
+        <v>5.897217159771081</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.29652140178456</v>
+        <v>4.30997369050467</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.876266790839658</v>
+        <v>3.889822837191261</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.747609744737559</v>
+        <v>5.737180109039407</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>179</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.5791873781140495</v>
+        <v>0.5917096677896723</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.554205943920707</v>
+        <v>4.567115753496758</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.511292544586695</v>
+        <v>7.524299676004297</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.289590369931652</v>
+        <v>4.302569512330116</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.63385071910529</v>
+        <v>2.646961523480229</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1379965674354722</v>
+        <v>0.1510394637298376</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.6119220680403501</v>
+        <v>0.6249883223408261</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.848649283783928</v>
+        <v>6.861830293079166</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.904967833355812</v>
+        <v>7.918166572310575</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.378864994696606</v>
+        <v>5.392270122349437</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.939474798870584</v>
+        <v>2.952932092580802</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.297880302584794</v>
+        <v>1.311332591304904</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.436284909516992</v>
+        <v>1.449840955868595</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.68600624179328</v>
+        <v>1.675576606095127</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>186</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.033443400220136</v>
+        <v>5.045965689895759</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.647676238868812</v>
+        <v>6.660586048444863</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.037515048372946</v>
+        <v>-5.024507916955343</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.756724281356838</v>
+        <v>-2.743745138958374</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.682242270622595</v>
+        <v>-1.669131466247656</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3095315157025951</v>
+        <v>-0.2964886194082297</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.218637992831539</v>
+        <v>1.231704247132015</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.7514545940500383</v>
+        <v>0.7646356033452761</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.303357933674199</v>
+        <v>2.316556672628963</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.06613597445272</v>
+        <v>3.079541102105551</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.011920284543741</v>
+        <v>5.025377578253959</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.97103462468484</v>
+        <v>3.98448691340495</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.013145605137822</v>
+        <v>3.026701651489425</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.112329303005509</v>
+        <v>1.101899667307357</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>153</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.369306777829237</v>
+        <v>4.38182906750486</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.75773316486498</v>
+        <v>2.770642974441031</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.016459229510239</v>
+        <v>3.029466360927842</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1212614940914634</v>
+        <v>-0.1082823516929992</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.313277480405425</v>
+        <v>-1.300166676030486</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.559327856003002</v>
+        <v>3.572370752297367</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.474594138730772</v>
+        <v>3.487660393031248</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.700221197465567</v>
+        <v>1.713402206760804</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.94641085376697</v>
+        <v>2.959609592721733</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.364259524948189</v>
+        <v>5.37766465260102</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.891532344421492</v>
+        <v>1.90498963813171</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.154673671701573</v>
+        <v>7.168125960421683</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.734419060756672</v>
+        <v>6.747975107108275</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.637735164274744</v>
+        <v>7.627305528576592</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>108</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.419364246135899</v>
+        <v>-3.406841956460276</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.463453431957376</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.907526767636561</v>
+        <v>2.920533899054163</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.815557678021861</v>
+        <v>5.828536820420325</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.203062388875622</v>
+        <v>6.216173193250562</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.712066905615274</v>
+        <v>2.72513315991575</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.652290914241256</v>
+        <v>9.665471923536494</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.665365102132974</v>
+        <v>8.678563841087737</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.74116584303097</v>
+        <v>8.754570970683801</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.24011622241704</v>
+        <v>12.25357351612726</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.27449937976253</v>
+        <v>12.28795166848264</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.076466991039815</v>
+        <v>9.090023037391418</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.25211424924204</v>
+        <v>10.24168461354389</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>87</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.276676622318746</v>
+        <v>7.289198911994369</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.380874002139748</v>
+        <v>-2.367964192563697</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.971383728045268</v>
+        <v>2.98439085946287</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.549912722721736</v>
+        <v>6.5628918651202</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.563215645580598</v>
+        <v>2.576326449955538</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.010082870652575</v>
+        <v>4.02312576694694</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.4770732913113704</v>
+        <v>0.4901395456118465</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.757016329311419</v>
+        <v>5.770197338606657</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.098315293703855</v>
+        <v>1.111514032658619</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.05066046603671</v>
+        <v>-2.037255338383879</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.105988502997974</v>
+        <v>-1.092531209287756</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.0778199417037797</v>
+        <v>0.09127223042388977</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.105841192827853</v>
+        <v>3.119397239179456</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.654413099816843</v>
+        <v>5.643983464118691</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>81</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>10.469524642753</v>
+        <v>10.48204693242862</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8.857951029788708</v>
+        <v>8.870860839364759</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.524810718253875</v>
+        <v>3.537817849671477</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.59333545579964</v>
+        <v>8.606314598198104</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.351210537023753</v>
+        <v>4.364321341398693</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.648652474739421</v>
+        <v>4.661695371033787</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.798486658701719</v>
+        <v>5.811552913002195</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.862167457451115</v>
+        <v>2.875348466746352</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.03573547250334</v>
+        <v>4.048934211458104</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.889313991179122</v>
+        <v>6.902719118831953</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.449992765626973</v>
+        <v>5.463450059337191</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.188079626676114</v>
+        <v>9.201531915396224</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>10.00239291696574</v>
+        <v>10.01594896331734</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>12.72125005171117</v>
+        <v>12.71082041601301</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>45</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-14.7156605424322</v>
+        <v>-14.70313825275657</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-16.32723415539643</v>
+        <v>-16.31432434582037</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-14.49988063977082</v>
+        <v>-14.48687350835322</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.92518306271888</v>
+        <v>-9.912203920320415</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.46360427779101</v>
+        <v>-10.45049347341607</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.9449487710357403</v>
+        <v>0.9579916673301057</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.749103942652347</v>
+        <v>9.762170196952823</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.281920543870847</v>
+        <v>9.295101553166084</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.44314287991077</v>
+        <v>11.45634161886554</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.81523991710505</v>
+        <v>12.82864504475788</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.44683736141022</v>
+        <v>14.46039340776183</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that BB Pct-20 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that BB Pct-20 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4075</v>
+        <v>4076</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.07171620670704471</v>
+        <v>-0.07201409852163465</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.03111910224690462</v>
+        <v>-0.03143676156295783</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02117285709827854</v>
+        <v>-0.02149548045990457</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.02446226848523025</v>
+        <v>-0.02478346021273126</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1822896624901418</v>
+        <v>-0.1825756167589603</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.09187056115465708</v>
+        <v>-0.09217701261331968</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1142527996852962</v>
+        <v>-0.114554433629273</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1269933933449821</v>
+        <v>-0.1272948755997803</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02744535538335668</v>
+        <v>-0.02777175204030868</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.005985328734070094</v>
+        <v>-0.006322275503556796</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0482284052227584</v>
+        <v>0.04787676765047877</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.07189942881820599</v>
+        <v>0.07154202686455591</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1070707056474944</v>
+        <v>0.1067019679776706</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.02716537398643482</v>
+        <v>0.0274222648360265</v>
       </c>
     </row>
     <row r="7">
@@ -2266,205 +2266,205 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4039</v>
+        <v>4040</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.09955875456338248</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.05445486514716436</v>
+        <v>0.05399856741860276</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.006053479276999951</v>
+        <v>-0.00649829235717192</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.03522395072963747</v>
+        <v>-0.03566071044387087</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2143728329074293</v>
+        <v>-0.2147699751586458</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.02245474253724922</v>
+        <v>0.02200132916584607</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.09820753095671364</v>
+        <v>-0.09863204338983422</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1563434308579161</v>
+        <v>-0.156757621876487</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.03064544847698158</v>
+        <v>-0.03109142604589721</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.02330873289090363</v>
+        <v>0.02284220928145686</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1293166549129339</v>
+        <v>0.1288220023082758</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1281659639413562</v>
+        <v>0.1276716457582907</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.216914369110988</v>
+        <v>0.2163943976158222</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1093396350636411</v>
+        <v>0.1096714122237756</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003109</t>
+          <t>X &gt; -0.0003048</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3997</v>
+        <v>3998</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.09942335761645893</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1978067248452291</v>
+        <v>0.1971746843818636</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.09093772350262697</v>
+        <v>0.09032778872834513</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03516410751099386</v>
+        <v>0.03456920010540898</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.09027538224547271</v>
+        <v>-0.09084508032623972</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.09600994456881295</v>
+        <v>0.09539667093579851</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.02493921848761005</v>
+        <v>0.02434248159701013</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.05385540194757965</v>
+        <v>-0.0544377963732714</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.09881504382879314</v>
+        <v>0.09819356324057793</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.06231703671403466</v>
+        <v>0.06169518635375226</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2215977038985741</v>
+        <v>0.2209335279762072</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1950906386883773</v>
+        <v>0.1944331499641265</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2892029886682934</v>
+        <v>0.2885171053528879</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1778919158253345</v>
+        <v>0.1783195977026537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.04184</t>
+          <t>X &gt; 0.04185</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3919</v>
+        <v>3920</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1282297749403938</v>
+        <v>-0.1290218022099197</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.05423507776446002</v>
+        <v>0.05337091811087902</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1741808942237455</v>
+        <v>-0.1749935795819226</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.0301009100648244</v>
+        <v>-0.03094861921778147</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.09643976093202866</v>
+        <v>-0.09727948059916258</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.03968750771819884</v>
+        <v>-0.04053741164705826</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.03410769486393406</v>
+        <v>-0.0349607766487523</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1561544738220206</v>
+        <v>-0.1569842565356296</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.07718977083838041</v>
+        <v>0.07629915602050374</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.05686339120366313</v>
+        <v>0.05596410693933507</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.3763656794212693</v>
+        <v>0.3753812785162722</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3231831055694414</v>
+        <v>0.3222123442527476</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3510323727480937</v>
+        <v>0.3500474075918021</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.2835848624937469</v>
+        <v>0.2842016203466358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.08399</t>
+          <t>X &gt; 0.084</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3828</v>
+        <v>3829</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4236648237246783</v>
+        <v>-0.4246953121585051</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.016470266507568</v>
+        <v>-0.01764234749821014</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2930559458401092</v>
+        <v>-0.2941651750198915</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2529000449434164</v>
+        <v>-0.2540174713030225</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3341628739164904</v>
+        <v>-0.3352714248954669</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2310447407242151</v>
+        <v>-0.2321742609124584</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1190693153514388</v>
+        <v>-0.1202304518711941</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.232946435784875</v>
+        <v>-0.2340886539902343</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.007365855821703349</v>
+        <v>0.006159041922380482</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.08501491130592598</v>
+        <v>0.08376867869706217</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4691831907166488</v>
+        <v>0.4678316155628721</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3878346471447998</v>
+        <v>0.386504410731547</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.400233954660564</v>
+        <v>0.3988906517421</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.3252594948011023</v>
+        <v>0.3261278972559296</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3728</v>
+        <v>3729</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4217997209049713</v>
+        <v>-0.4231928878299129</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.06757877809401691</v>
+        <v>-0.06911361785105186</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2875243947855282</v>
+        <v>-0.2890125457863704</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2765295938406922</v>
+        <v>-0.2780177148584713</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5328814757811244</v>
+        <v>-0.5343172651050665</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.06028558537636286</v>
+        <v>-0.06184004557092493</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.02331908278273431</v>
+        <v>-0.02488666719184351</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.04736589307494654</v>
+        <v>-0.04894128485267402</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3082201189499543</v>
+        <v>0.3065469393440097</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4376050475087609</v>
+        <v>0.4358718804872623</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.6232326543140161</v>
+        <v>0.6214429933215513</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5120130328257844</v>
+        <v>0.5102533054184164</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6164985753192198</v>
+        <v>0.6146978462485677</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5060484409444967</v>
+        <v>0.5071713392076305</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3599</v>
+        <v>3600</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3893408672753154</v>
+        <v>-0.3912398611460333</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.06280861515033109</v>
+        <v>0.06072179666760036</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3447559860312026</v>
+        <v>-0.3467461198181923</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1717887706712204</v>
+        <v>-0.1738228800003156</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4457427355392554</v>
+        <v>-0.4477226227649567</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05003012801858375</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.008707112995665511</v>
+        <v>-0.01080210998123476</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.09406417154843894</v>
+        <v>0.09192166778984046</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3813596760631768</v>
+        <v>0.3791340368035705</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.6013440895539333</v>
+        <v>0.5990236364461268</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7732356827991964</v>
+        <v>0.7708584946945578</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.6846117970951653</v>
+        <v>0.6822593576265348</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.8635040280768891</v>
+        <v>0.8610845737959565</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7679982911055419</v>
+        <v>0.7694623913216958</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>3445</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5987319273838239</v>
+        <v>-0.6012167824140491</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.03271954830724155</v>
+        <v>0.02996903636710613</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4622540116955705</v>
+        <v>-0.4648827676124725</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2874039981882177</v>
+        <v>-0.2900781766317166</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5495199067127601</v>
+        <v>-0.5521469508657617</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.149424860997236</v>
+        <v>-0.1521540996358368</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.07139377812674752</v>
+        <v>0.06859481392204003</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1997949400060932</v>
+        <v>0.1969335503327585</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5027736907738074</v>
+        <v>0.4998198797350852</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6548893112788079</v>
+        <v>0.6518466168721773</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7567006920041806</v>
+        <v>0.7536164825275904</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.6625391897408122</v>
+        <v>0.6594824682118698</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7812995449290128</v>
+        <v>0.7781853726808947</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7407451152314195</v>
+        <v>0.7303154795332674</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3307</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6103410017405579</v>
+        <v>-0.6134461510162836</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.0664344768752585</v>
+        <v>-0.06980625134750085</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5354549539101043</v>
+        <v>-0.5387119652549686</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4190846844853979</v>
+        <v>-0.4223704027509925</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4887425382234269</v>
+        <v>-0.4920428635782912</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1145295364812071</v>
+        <v>-0.1179258791756936</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1190271408278676</v>
+        <v>0.1155531514220698</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2420654714070594</v>
+        <v>0.2385230912148373</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4092155669136801</v>
+        <v>0.4056169811843588</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6332996686995358</v>
+        <v>0.6295779619698649</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8989926872772429</v>
+        <v>0.8951758435302466</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.7995116955850037</v>
+        <v>0.7957250810611285</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.940806383350214</v>
+        <v>0.9369485602541019</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.797422181910143</v>
+        <v>0.7869925462119909</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>3138</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7627301588889139</v>
+        <v>-0.7666303162486372</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3566002432123483</v>
+        <v>-0.3607588400160893</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.8297185806669134</v>
+        <v>-0.8337604206785088</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6188328472777513</v>
+        <v>-0.6229337158929127</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7268086586424829</v>
+        <v>-0.7309201174791156</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2849070389727544</v>
+        <v>-0.2891378150935111</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1296389427720683</v>
+        <v>-0.1339281915119841</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2480426175677053</v>
+        <v>0.243593793417773</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.236520785036511</v>
+        <v>0.2320683322115826</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7416376524199819</v>
+        <v>0.7369545003452771</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.000986044134329</v>
+        <v>0.9962014944240849</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.9898878083440792</v>
+        <v>0.9851069314231893</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.175114395614592</v>
+        <v>1.188670441966195</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9149568241305275</v>
+        <v>0.9045271884323753</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2948</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6002672586819102</v>
+        <v>-0.6052823705140682</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.0299358425418319</v>
+        <v>-0.03530699175233565</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3050227236679746</v>
+        <v>-0.3103432411905516</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.05490669498058764</v>
+        <v>-0.06030195069178745</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4056790539890471</v>
+        <v>-0.4110123679451476</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.01181109560207716</v>
+        <v>0.006362990582928774</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2843342949558618</v>
+        <v>0.2787823051666791</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4118576649973846</v>
+        <v>0.4062126642771844</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.5052897725661225</v>
+        <v>0.4996037898809931</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.166093313736674</v>
+        <v>1.160095138919836</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.319969481374834</v>
+        <v>1.313895282451114</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.320431336142242</v>
+        <v>1.333883624862352</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.375074961289613</v>
+        <v>1.388631007641216</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.353425872941749</v>
+        <v>1.342996237243597</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2748</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.09866328392550372</v>
+        <v>-0.08614099424988098</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5592348907822071</v>
+        <v>0.5523100679838251</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5110126064165428</v>
+        <v>0.5040520814834366</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6612479014817936</v>
+        <v>0.6542448814225068</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.002525466421545275</v>
+        <v>-0.009358549898330182</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2222420526894737</v>
+        <v>0.2352849489838391</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4845940674554399</v>
+        <v>0.4776094734386049</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.6920215539718484</v>
+        <v>0.6848992025057115</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.7240935286314993</v>
+        <v>0.7169476794715735</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.386321916134648</v>
+        <v>1.378824908142548</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.399909203170779</v>
+        <v>1.413366496880997</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.179561647270205</v>
+        <v>1.193013935990315</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.159598157140451</v>
+        <v>1.173154203492054</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.372929387524458</v>
+        <v>1.362499751826306</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2574</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.333827365305126</v>
+        <v>0.3463496549807488</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.9511678421066705</v>
+        <v>0.9427545766342007</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7714371896865444</v>
+        <v>0.7630296299652599</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6129238693391983</v>
+        <v>0.6045919453126629</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.01825073470786975</v>
+        <v>0.01006402087539016</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.04416435589910606</v>
+        <v>0.05720725219347145</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3686874376723779</v>
+        <v>0.3603944879622034</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5828177143332169</v>
+        <v>0.5743668487293903</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6988063103314701</v>
+        <v>0.6902960702112679</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.385558487423623</v>
+        <v>1.376649359752491</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.064255046555928</v>
+        <v>1.077712340266146</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.098638203901359</v>
+        <v>1.112090492621469</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.066883981456847</v>
+        <v>1.08044002780845</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.510855507983322</v>
+        <v>1.50042587228517</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2415</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1316133540355864</v>
+        <v>0.1441356437112091</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.147262673939082</v>
+        <v>1.137331526670529</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7110374743731001</v>
+        <v>0.7240446057907022</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.4503973169988598</v>
+        <v>0.4407048196851022</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1602177237719573</v>
+        <v>0.1733285281468966</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1680444360014803</v>
+        <v>0.1810873322958457</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6211675660605991</v>
+        <v>0.6342338203610751</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.128866827903209</v>
+        <v>1.118758060314505</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.132583873699581</v>
+        <v>1.122456409152491</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.607510448506012</v>
+        <v>1.620915576158843</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.485572859178085</v>
+        <v>1.499030152888302</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.561363884018341</v>
+        <v>1.574816172738451</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.555187948021675</v>
+        <v>1.568743994373278</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.929132882782433</v>
+        <v>1.918703247084281</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2268</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5902621203186627</v>
+        <v>0.6027844099942854</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.426059023194213</v>
+        <v>1.414505805917237</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.075262595134419</v>
+        <v>1.088269726552021</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7009192300500757</v>
+        <v>0.6896275276987751</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3829565687697993</v>
+        <v>0.3960673731447386</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.5040316634519542</v>
+        <v>0.5170745597463196</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.212948739830466</v>
+        <v>1.226014994130942</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.583507845458136</v>
+        <v>1.596688854753374</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.831149934584474</v>
+        <v>1.844348673539237</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.391959493824629</v>
+        <v>2.40536462147746</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.275389591023796</v>
+        <v>2.288846884734014</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.353864459127607</v>
+        <v>2.367316747847717</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.065884980457845</v>
+        <v>2.079441026809448</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.491973155767631</v>
+        <v>2.481543520069479</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>2130</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.049499267776888</v>
+        <v>1.06202155745251</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.622687597342193</v>
+        <v>1.60944644514889</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.556457388398194</v>
+        <v>1.569464519815796</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.123330239315557</v>
+        <v>1.136309381714021</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6318573810508923</v>
+        <v>0.6449681854258316</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6945575347289932</v>
+        <v>0.7076004310233586</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.783532737644514</v>
+        <v>1.79659899194499</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.114471404590716</v>
+        <v>2.127652413885954</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.476006729676016</v>
+        <v>2.489205468630779</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.940435535258416</v>
+        <v>2.953840662911247</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.735682210940837</v>
+        <v>2.749139504651055</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.004807152323828</v>
+        <v>3.018259441043938</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.866242682223998</v>
+        <v>2.879798728575601</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.16291237130779</v>
+        <v>3.152482735609638</v>
       </c>
     </row>
     <row r="22">
@@ -3049,98 +3049,98 @@
         <v>1985</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.461221629412186</v>
+        <v>1.473743919087809</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.965517034080172</v>
+        <v>1.978426843656223</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.973670997508776</v>
+        <v>1.986678128926378</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.852034961350533</v>
+        <v>1.865014103748997</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.162480245018912</v>
+        <v>1.175591049393852</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.258410847721983</v>
+        <v>1.271453744016348</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.231611639265822</v>
+        <v>2.244677893566298</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.570473580534703</v>
+        <v>2.583654589829941</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.710985029364998</v>
+        <v>2.724183768319762</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.27143918942523</v>
+        <v>3.284844317078061</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.865174530095054</v>
+        <v>2.878631823805271</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.403336024971971</v>
+        <v>3.416788313692081</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.033459247780222</v>
+        <v>3.047015294131825</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.081669245043919</v>
+        <v>3.071239609345767</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.632</t>
+          <t>X &gt; 0.6319</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1834</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.977663097456329</v>
+        <v>1.990185387131952</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.165435176967534</v>
+        <v>2.178344986543586</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.716040843326233</v>
+        <v>1.729047974743835</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.846293975933733</v>
+        <v>1.859273118332197</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.47144964199569</v>
+        <v>1.484560446370629</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.38721219039838</v>
+        <v>1.400255086692745</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.665619149243881</v>
+        <v>2.678685403544357</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.798217647954196</v>
+        <v>2.811398657249434</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.118897151084873</v>
+        <v>3.132095890039636</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.631912642174719</v>
+        <v>3.64531776982755</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.427159317857139</v>
+        <v>3.440616611567357</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.006798745649682</v>
+        <v>4.020251034369792</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.641069761749492</v>
+        <v>3.654625808101095</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.727214212891653</v>
+        <v>3.716784577193501</v>
       </c>
     </row>
     <row r="24">
@@ -3153,98 +3153,98 @@
         <v>1681</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.176401061110667</v>
+        <v>2.18892335078629</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.587433040055984</v>
+        <v>2.600342849632035</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.895122334649159</v>
+        <v>1.908129466066761</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.263329066304848</v>
+        <v>2.276308208703313</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.903373050518823</v>
+        <v>1.916483854893762</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.02234978894834</v>
+        <v>2.035392685242705</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.008407267392897</v>
+        <v>3.021473521693373</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.017131066707769</v>
+        <v>3.030312076003007</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.491526778383879</v>
+        <v>3.504725517338642</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.069123187645076</v>
+        <v>4.082528315297907</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.983346662851581</v>
+        <v>3.996803956561799</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.434148618531339</v>
+        <v>4.447600907251449</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.192359206872574</v>
+        <v>4.205915253224177</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.323103739624777</v>
+        <v>4.312674103926625</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.7163</t>
+          <t>X &gt; 0.7162</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1513</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.901802922354463</v>
+        <v>1.914325212030086</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.339138760811231</v>
+        <v>2.352048570387282</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.745988494399704</v>
+        <v>1.758995625817306</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.677960067192259</v>
+        <v>1.690939209590724</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.536101971749972</v>
+        <v>1.549212776124911</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.569168496379049</v>
+        <v>1.582211392673415</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.409748724909811</v>
+        <v>2.422814979210287</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.264442391561218</v>
+        <v>3.277623400856456</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.864381038095381</v>
+        <v>3.877579777050144</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.600508331586951</v>
+        <v>4.613913459239782</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.065285740911136</v>
+        <v>4.078743034621354</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.694513577701386</v>
+        <v>4.707965866421496</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.340352820028123</v>
+        <v>4.353908866379726</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.193511032674536</v>
+        <v>4.183081396976384</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1306</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.71789399219432</v>
+        <v>1.730416281869942</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.709689445079974</v>
+        <v>2.722599254656025</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.085111703261333</v>
+        <v>2.098118834678935</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.215364835868833</v>
+        <v>2.228343978267297</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.753513299204023</v>
+        <v>1.766624103578962</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.510373307363778</v>
+        <v>2.523416203658144</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.421045409387062</v>
+        <v>3.434111663687538</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.71496461397463</v>
+        <v>4.728145623269867</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.113382798236429</v>
+        <v>5.126581537191193</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.258663432504065</v>
+        <v>5.272068560156896</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.824201072964435</v>
+        <v>4.837658366674653</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.471141657568666</v>
+        <v>5.484593946288776</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.050887046623764</v>
+        <v>5.064443092975367</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.300608378900051</v>
+        <v>5.290178743201899</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1108</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.831471427082441</v>
+        <v>2.843993716758064</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.84444655058028</v>
+        <v>2.857356360156331</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.810588674308605</v>
+        <v>2.823595805726207</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.66286346756592</v>
+        <v>3.675842609964384</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.763431422168836</v>
+        <v>2.776542226543775</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.699862529559596</v>
+        <v>2.712905425853961</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.69816130326204</v>
+        <v>3.711227557562516</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.397042886429993</v>
+        <v>5.410223895725231</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.787306538153835</v>
+        <v>5.800505277108599</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.929961136519417</v>
+        <v>5.943366264172248</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.725207812201837</v>
+        <v>5.738665105912055</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.120601799872169</v>
+        <v>6.134054088592279</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.880852604089725</v>
+        <v>5.894408650441328</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.401332059109698</v>
+        <v>6.390902423411546</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>923</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.652823868305731</v>
+        <v>2.665346157981354</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.96649402565567</v>
+        <v>3.979403835231722</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.02991350974164</v>
+        <v>3.042920641159242</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.376851366076117</v>
+        <v>3.389830508474581</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.62174542727697</v>
+        <v>2.634856231651909</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.919187364992631</v>
+        <v>2.932230261286996</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.701192542628263</v>
+        <v>3.714258796928739</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.509198742980018</v>
+        <v>5.522379752275256</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.881568304251672</v>
+        <v>5.894767043206436</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.006524375995141</v>
+        <v>6.019929503647973</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.69342868981407</v>
+        <v>5.706885983524288</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.486208380203927</v>
+        <v>6.499660668924037</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.282638492986003</v>
+        <v>6.296194539337606</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.53235982526229</v>
+        <v>6.521930189564138</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>744</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.151722970112601</v>
+        <v>3.164245259788224</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.825095593707495</v>
+        <v>3.838005403283546</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.951732263454993</v>
+        <v>1.964739394872595</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.157254213266789</v>
+        <v>3.170233355665253</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.61883299819462</v>
+        <v>2.631943802569559</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.588317946662968</v>
+        <v>3.601360842957334</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.44444444444445</v>
+        <v>4.457510698744926</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.186938465017789</v>
+        <v>5.200119474313027</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.39475578313656</v>
+        <v>5.407954522091323</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.157533823915088</v>
+        <v>6.170938951567919</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.356006306049117</v>
+        <v>6.369463599759335</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.734475484899924</v>
+        <v>7.747927773620034</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.448629476105559</v>
+        <v>7.462185522457162</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.698350808381846</v>
+        <v>7.687921172683694</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>558</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.52448282674343</v>
+        <v>2.537005116419053</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.884235378653727</v>
+        <v>2.897145188229779</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.281481367397639</v>
+        <v>4.294488498815241</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.128580378141329</v>
+        <v>5.141559520539793</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.052524754467015</v>
+        <v>4.065635558841954</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.887601100784821</v>
+        <v>4.900643997079186</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.519713261648754</v>
+        <v>5.53277951594923</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.665433088673701</v>
+        <v>6.678614097968939</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.425221732957354</v>
+        <v>6.438420471912117</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.187999773735875</v>
+        <v>7.201404901388706</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.804034979884243</v>
+        <v>6.817492273594461</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.988955771638288</v>
+        <v>9.002408060358398</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.927124099761478</v>
+        <v>8.940680146113081</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>9.893691310173963</v>
+        <v>9.883261674475811</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>405</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.827549334111012</v>
+        <v>1.840071623786635</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.932025103862806</v>
+        <v>2.944934913438857</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.75937861948843</v>
+        <v>4.772385750906032</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.111853974318159</v>
+        <v>7.124833116716623</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.07960559875216</v>
+        <v>6.092716403127099</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.402436111774534</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.292313819195542</v>
+        <v>6.305380073496018</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>8.541179803130099</v>
+        <v>8.554360812425337</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.73943917620705</v>
+        <v>7.752637915161813</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.876968312166781</v>
+        <v>7.890373439819612</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.659869308836846</v>
+        <v>8.673326602547064</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.681906787169936</v>
+        <v>9.695359075890046</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.755479336718857</v>
+        <v>9.769035383070459</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.74594140973589</v>
+        <v>10.73551177403774</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>297</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.735517908746253</v>
+        <v>3.748040198421876</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.470745642583346</v>
+        <v>3.483655452159397</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.432779292889116</v>
+        <v>5.445786424306718</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.583234445698629</v>
+        <v>7.596213588097093</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.034712220525449</v>
+        <v>6.047823024900389</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.005554831641781</v>
+        <v>7.018597727936147</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.594221787770188</v>
+        <v>7.607288042070664</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.137139399089691</v>
+        <v>8.150320408384928</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.402738839506718</v>
+        <v>7.415937578461481</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.562714664579794</v>
+        <v>7.576119792232625</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>7.357961340262214</v>
+        <v>7.371418633972432</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.739145844408995</v>
+        <v>8.752598133129105</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.92551492264275</v>
+        <v>10.9150852869446</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>210</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>5.907897876401819</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.452500312610134</v>
+        <v>6.465507444027736</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.011324873789057</v>
+        <v>8.024304016187521</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.472903658716888</v>
+        <v>7.486014463091827</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.246536072623023</v>
+        <v>8.259578968917388</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.54275473630313</v>
+        <v>10.55582099060361</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.123190385140681</v>
+        <v>9.136371394435919</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.01457145133933</v>
+        <v>10.02777019029409</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.54539864726378</v>
+        <v>11.55880377491661</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.86445484675572</v>
+        <v>10.87791214046594</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.32740943267258</v>
+        <v>12.34086172139269</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.85953577410863</v>
+        <v>12.87309182046023</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>13.10925710638492</v>
+        <v>13.09882747068676</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>129</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.881035219434779</v>
+        <v>-2.868512929759156</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.034522950546702</v>
+        <v>4.047432760122753</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.29081703464778</v>
+        <v>8.303824166065382</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.645876368805666</v>
+        <v>7.658855511204131</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.433036549082345</v>
+        <v>9.446147353457285</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.50567228524761</v>
+        <v>10.51871518154198</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13.52171376177377</v>
+        <v>13.53478001607425</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.05453036299227</v>
+        <v>13.06771137228751</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.76872427525959</v>
+        <v>13.78192301421436</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.46898668713089</v>
+        <v>14.48239181478372</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.26423336281331</v>
+        <v>14.27769065652353</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.29861652015875</v>
+        <v>14.31206880887886</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.65355570766345</v>
+        <v>14.66711175401505</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>13.35288944304051</v>
+        <v>13.34245980734236</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3.458942632170981</v>
+        <v>3.471464921846604</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>14.94260711444482</v>
+        <v>14.95551692402087</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>20.50011936022918</v>
+        <v>20.51312649164678</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>17.05894392140811</v>
+        <v>17.07192306380657</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>20.09195127776451</v>
+        <v>20.10506208213945</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>15.6274884535754</v>
+        <v>15.64053134986976</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>15.54275473630312</v>
+        <v>15.55582099060359</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>15.07557133752162</v>
+        <v>15.08875234681685</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>15.01457145133931</v>
+        <v>15.02777019029408</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>15.35492245678759</v>
+        <v>15.36832758444042</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>16.3406453229462</v>
+        <v>16.35410261665642</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>16.37502848029163</v>
+        <v>16.38848076901174</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>14.76429767887054</v>
+        <v>14.77785372522214</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.01401901114683</v>
+        <v>15.00358937544868</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that BB Pct-20 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that BB Pct-20 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.418797590635293</v>
+        <v>5.431707400211344</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.452500312610134</v>
+        <v>1.465507444027736</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.56814175395499</v>
+        <v>10.58125255832993</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.294155120242074</v>
+        <v>7.307198016536439</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.590373783922182</v>
+        <v>9.603440038222658</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.123190385140681</v>
+        <v>9.136371394435919</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.490761927529796</v>
+        <v>5.503960666484559</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.7118927973199334</v>
+        <v>-0.6983367509683305</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.918780915908734</v>
+        <v>1.908351280210582</v>
       </c>
     </row>
     <row r="7">
@@ -3963,202 +3963,202 @@
         <v>120</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.173228346456689</v>
+        <v>4.185750636132312</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8949880668257748</v>
+        <v>0.907897876401826</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5001193602291849</v>
+        <v>0.513126491646787</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.297039159503342</v>
+        <v>2.310018301901806</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.425284611097837</v>
+        <v>8.438395415472776</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.222726548813505</v>
+        <v>1.23576944510787</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.137992831541219</v>
+        <v>6.151059085841695</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.337476099426389</v>
+        <v>7.350657108721627</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.943142879910752</v>
+        <v>3.956341618865515</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.259684361549496</v>
+        <v>2.273089489202327</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.278402296101412</v>
+        <v>-1.264945002391194</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.244019138755981</v>
+        <v>-1.230566850035871</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.164273749700889</v>
+        <v>-4.150717703349287</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.414552417424595</v>
+        <v>-1.424982053122747</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003109</t>
+          <t>X &lt; -0.0003048</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>162</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.870444031939662</v>
+        <v>-2.857534222363611</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.03074483730169</v>
+        <v>-2.017737705884088</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.04863985284233507</v>
+        <v>-0.03566071044387087</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.116642635789205</v>
+        <v>3.129753440164144</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.9069030808161216</v>
+        <v>-0.8938601845217562</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.477499004380732</v>
+        <v>1.490565258681208</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.862167457451086</v>
+        <v>2.875348466746324</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2852521818176399</v>
+        <v>-0.2720534428628767</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.7164744850062803</v>
+        <v>0.7298796126591114</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.191982543014994</v>
+        <v>-3.178525249304776</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.540315435052278</v>
+        <v>-2.526863146332168</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.812421897849042</v>
+        <v>-4.798865851497439</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.710848713720893</v>
+        <v>-2.721278349419045</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.04184</t>
+          <t>X &lt; 0.04185</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>240</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.506561679790032</v>
+        <v>2.519083969465655</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.4783214001590963</v>
+        <v>0.4912312097351474</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.000119360229171</v>
+        <v>3.013126491646773</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.047039159503349</v>
+        <v>1.060018301901813</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.175284611097837</v>
+        <v>2.188395415472776</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.639393215480169</v>
+        <v>1.652436111774534</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.971326164874554</v>
+        <v>1.98439241917503</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.587476099426389</v>
+        <v>3.600657108721627</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1931428799107593</v>
+        <v>0.2063416188655225</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.5930176948828247</v>
+        <v>0.6064228225356558</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.611735629434747</v>
+        <v>-4.59827833572453</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.744019138755988</v>
+        <v>-3.730566850035878</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.164273749700889</v>
+        <v>-4.150717703349287</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.497885750757938</v>
+        <v>-3.50831538645609</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.08399</t>
+          <t>X &lt; 0.084</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>331</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.210489172237153</v>
+        <v>5.223011461912776</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.18199713026987</v>
+        <v>1.194906939845922</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.506161656301693</v>
+        <v>3.519168787719295</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.334299985283806</v>
+        <v>3.34727912768227</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.306452788338518</v>
+        <v>4.319563592713457</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.395435511552684</v>
+        <v>3.408478407847049</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.404357383404268</v>
+        <v>2.417423637704744</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.447748002749655</v>
+        <v>3.460929012044893</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.969829687564328</v>
+        <v>0.9830284265190912</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1197045025364005</v>
+        <v>0.1331096301892316</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.314656072536465</v>
+        <v>-4.301198778826247</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.373928504314897</v>
+        <v>-3.360476215594787</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.492068311634419</v>
+        <v>-3.478512265282816</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.94023217573276</v>
+        <v>-2.950661811430912</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>431</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.887072120625291</v>
+        <v>3.899594410300914</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.347424261721365</v>
+        <v>1.360334071297416</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.576685485519192</v>
+        <v>2.589692616936794</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.706938618126692</v>
+        <v>2.719917760525156</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.952740140873559</v>
+        <v>4.965850945248498</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.07384797186068</v>
+        <v>1.086890868155045</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.9891142545884009</v>
+        <v>1.002180508888877</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9859679787767348</v>
+        <v>0.9991489880719726</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.859254645224595</v>
+        <v>-1.846055906269832</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.941398391737437</v>
+        <v>-2.927993264084606</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.538263084964527</v>
+        <v>-4.524805791254309</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.575805681679427</v>
+        <v>-3.562353392959317</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.460097415594156</v>
+        <v>-4.446541369242553</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.746338960348041</v>
+        <v>-3.756768596046193</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>560</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.685133108361455</v>
+        <v>2.697655398037078</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1807023525400524</v>
+        <v>0.1936121621161035</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.285833645943462</v>
+        <v>2.298840777361065</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.344658207122393</v>
+        <v>1.357637349520857</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.1276655634788</v>
+        <v>3.140776367853739</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.7465360726230301</v>
+        <v>0.7595789689173955</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6618023553507513</v>
+        <v>0.6748686096512273</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1625239005736034</v>
+        <v>-0.1493428912783656</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.830666643898773</v>
+        <v>-1.81746790494401</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.216506114640978</v>
+        <v>-3.203100986988147</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.314116581815703</v>
+        <v>-4.300659288105486</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.744019138755988</v>
+        <v>-3.730566850035878</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.878559463986598</v>
+        <v>-4.865003417634995</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.450266703138887</v>
+        <v>-4.460696338837039</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.031037204265552</v>
+        <v>3.043559493941174</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.3005824724201744</v>
+        <v>0.3134922819962256</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.283336143445965</v>
+        <v>2.296343274863567</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.574428436892624</v>
+        <v>1.587407579291089</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.854189040002275</v>
+        <v>2.867299844377214</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.053728879815829</v>
+        <v>1.066771776110194</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1298343233827168</v>
+        <v>0.1429005776831929</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.936810500042633</v>
+        <v>-1.923611761087869</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.647075545210406</v>
+        <v>-2.633670417557575</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.131549149248272</v>
+        <v>-3.118091855538054</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.677585572322421</v>
+        <v>-2.664133283602311</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.237700323127456</v>
+        <v>-3.224144276775853</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.193263902018437</v>
+        <v>-3.138268766409475</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.488976685651686</v>
+        <v>2.501498975327308</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.642936484176289</v>
+        <v>0.6558462937523402</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.123800485668809</v>
+        <v>2.136807617086411</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.78512044125403</v>
+        <v>1.798099583652494</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.067332285970835</v>
+        <v>2.080443090345774</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7235081041085394</v>
+        <v>0.7365510004029048</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.06462537869714424</v>
+        <v>-0.05155912439666821</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6490420717342147</v>
+        <v>-0.6358610624389769</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.178975134938796</v>
+        <v>-1.165776395984032</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.029100319966723</v>
+        <v>-2.015695192313892</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.054486704073284</v>
+        <v>-3.041029410363066</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.668403663961143</v>
+        <v>-2.654951375241033</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.205891569161615</v>
+        <v>-3.192335522810012</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.776054764842442</v>
+        <v>-2.732133284072347</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.44302306786431</v>
+        <v>2.455545357539933</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.417959718829671</v>
+        <v>1.430869528405722</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.587118382712077</v>
+        <v>2.60012551412968</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.033109540735019</v>
+        <v>2.046088683133483</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.374453721557281</v>
+        <v>2.38756452593222</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.107868288793945</v>
+        <v>1.12091118508831</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.7298794395568606</v>
+        <v>0.7429456938573367</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.519317644464131</v>
+        <v>-0.5061366351688932</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3848141093365598</v>
+        <v>-0.3716153703817966</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.919201268949045</v>
+        <v>-1.905796141296214</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.710464857196243</v>
+        <v>-2.697007563486025</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.676081699850812</v>
+        <v>-2.662629411130702</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.239616215454312</v>
+        <v>-3.278283685753983</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.545796295975045</v>
+        <v>-2.511087728269523</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.542805501865807</v>
+        <v>1.55532779154143</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3430935033990821</v>
+        <v>0.3560033129751332</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.771948025797542</v>
+        <v>0.7849551572151441</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2432225752089963</v>
+        <v>0.2562017176074605</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.105130849428427</v>
+        <v>1.118241653803366</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1669879436514989</v>
+        <v>0.1800308399458643</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.4119797110178069</v>
+        <v>-0.3989134567173309</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7967907868997983</v>
+        <v>-0.7836097776045605</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9401629959816091</v>
+        <v>-0.9269642570268459</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.531639087105098</v>
+        <v>-2.518233959452267</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.901137057221682</v>
+        <v>-2.887679763511464</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.905189790033816</v>
+        <v>-2.93567393405565</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.033910713397262</v>
+        <v>-3.064567662129171</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.070208899670682</v>
+        <v>-3.04214376929437</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2607989679256235</v>
+        <v>0.2360917323449669</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.8564243625527652</v>
+        <v>-0.8435145529767141</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.9688071934431406</v>
+        <v>-0.9558000620255385</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.191661405468402</v>
+        <v>-1.178682263069938</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1060755715498232</v>
+        <v>0.1191863759247624</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2643170318696519</v>
+        <v>-0.289654283705687</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7024076396012973</v>
+        <v>-0.6893413853008212</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.169591038382798</v>
+        <v>-1.15641002908756</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.159919546473233</v>
+        <v>-1.14672080751847</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.434073000052393</v>
+        <v>-2.420667872399562</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.459448972197599</v>
+        <v>-2.484026274476008</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.033120341869932</v>
+        <v>-2.058006736881701</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.990052786528089</v>
+        <v>-2.015190456357075</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.481171836276474</v>
+        <v>-2.458976387400369</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4808597038577744</v>
+        <v>-0.501029166926557</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.337716335689954</v>
+        <v>-1.324806526113903</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.229440388198498</v>
+        <v>-1.216433256780896</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.9105080103079786</v>
+        <v>-0.8975288679095144</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.06050473688400615</v>
+        <v>0.07361554125894543</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0778765383247304</v>
+        <v>0.0565241620889978</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3844531512571763</v>
+        <v>-0.3713868969567002</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.7887038879870758</v>
+        <v>-0.775522878691838</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9126364362209785</v>
+        <v>-0.8994376972662153</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.014492269455339</v>
+        <v>-2.001087141802508</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.492508089552295</v>
+        <v>-1.513529017495046</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.549627204288441</v>
+        <v>-1.570617227869626</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.49403415323178</v>
+        <v>-1.515241962958612</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.282060303859936</v>
+        <v>-2.263569694989087</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1260680977342261</v>
+        <v>-0.1434017773986653</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.395371317087523</v>
+        <v>-1.382461507511472</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9610678543826978</v>
+        <v>-0.9786019738409593</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5454265939213201</v>
+        <v>-0.5324474515228559</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1393451242914594</v>
+        <v>-0.1574949954861253</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.09632107023411862</v>
+        <v>-0.1144114039307809</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.6644657162003469</v>
+        <v>-0.6822742474916339</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.417526759350046</v>
+        <v>-1.404345750054809</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.364175587785077</v>
+        <v>-1.350976848830314</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.01186407475867</v>
+        <v>-2.029369058539245</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.842225993869022</v>
+        <v>-1.859910677448411</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.948486492707879</v>
+        <v>-1.966113501438279</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.936480053425818</v>
+        <v>-1.954268677003348</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.515469848617258</v>
+        <v>-2.499480620457994</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6532700762562413</v>
+        <v>-0.667989073098731</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.528776391639013</v>
+        <v>-1.515866582062962</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.264741239455198</v>
+        <v>-1.279723140319568</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7662608580312877</v>
+        <v>-0.7532817156328235</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3817329327617998</v>
+        <v>-0.3973050930315196</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4768521768315779</v>
+        <v>-0.492300730330733</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.270682967545532</v>
+        <v>-1.285749760919749</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.762418470947885</v>
+        <v>-1.777372396020205</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.006224208696835</v>
+        <v>-2.021078869625086</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.669955040385418</v>
+        <v>-2.68471641797067</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.529722253862772</v>
+        <v>-2.544628379699915</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.625424315723762</v>
+        <v>-2.64028173915942</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.27738157211104</v>
+        <v>-2.292556055171794</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.845012491459507</v>
+        <v>-2.830901714856374</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.048068403502484</v>
+        <v>-1.060739732787042</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.532743437338858</v>
+        <v>-1.519833627762807</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.607723777025726</v>
+        <v>-1.620631470136658</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.108224858806288</v>
+        <v>-1.1213542471178</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.5900899391147902</v>
+        <v>-0.6036186437065609</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6096249484864487</v>
+        <v>-0.623079099216632</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.699269774876591</v>
+        <v>-1.712220246509794</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.091270829320543</v>
+        <v>-2.104156250806867</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.42116390475001</v>
+        <v>-2.433912271388373</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.900997717479861</v>
+        <v>-2.913734502931398</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.685882611062041</v>
+        <v>-2.698786615770445</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.969770000400501</v>
+        <v>-2.982535353972878</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.821909217681188</v>
+        <v>-2.83486344436357</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.186361190219081</v>
+        <v>-3.173750526029153</v>
       </c>
     </row>
     <row r="22">
@@ -4740,101 +4740,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.281732787516788</v>
+        <v>-1.29261621334971</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.634746608380091</v>
+        <v>-1.645828689670424</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.776768511624368</v>
+        <v>-1.787879912744806</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.622374759910571</v>
+        <v>-1.633536236618404</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.9914202293358159</v>
+        <v>-1.002996525919166</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.035904676362172</v>
+        <v>-1.047403558404113</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.875533074006697</v>
+        <v>-1.886673880855525</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.226744084059852</v>
+        <v>-2.237834408930823</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.309342969867437</v>
+        <v>-2.320416790920412</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.813777530094221</v>
+        <v>-2.824814748215452</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.442848782091318</v>
+        <v>-2.454109373373754</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.935195609344227</v>
+        <v>-2.946230607500276</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.595308232459516</v>
+        <v>-2.606600056290468</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.688701451463238</v>
+        <v>-2.677855616341141</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.632</t>
+          <t>X &lt; 0.6319</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.509691528079948</v>
+        <v>-1.518966479444138</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.559012788972261</v>
+        <v>-1.568577743786378</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.332072420592738</v>
+        <v>-1.341815741986089</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.393182111017715</v>
+        <v>-1.402881241477182</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.094852492586817</v>
+        <v>-1.10478802492694</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9886607922352155</v>
+        <v>-0.9985921658604227</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.950915115857285</v>
+        <v>-1.960456845005567</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.09517083322055</v>
+        <v>-2.104745978756938</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.305068851133598</v>
+        <v>-2.31457215204825</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.70310367337251</v>
+        <v>-2.712604359152472</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.541288894039567</v>
+        <v>-2.550904641721388</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.999498296469788</v>
+        <v>-3.008917365499798</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.708985701549558</v>
+        <v>-2.718616285214353</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.823154567962241</v>
+        <v>-2.813632096115015</v>
       </c>
     </row>
     <row r="24">
@@ -4844,101 +4844,101 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.429608532975934</v>
+        <v>-1.437577346746231</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.615052093816807</v>
+        <v>-1.623214126809742</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.265650025066122</v>
+        <v>-1.274022102730733</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.475736831922163</v>
+        <v>-1.484008750461932</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.228917238520175</v>
+        <v>-1.237381647764089</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.271910082991269</v>
+        <v>-1.280314189793621</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.898559817687484</v>
+        <v>-1.906731206461863</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.94191198430952</v>
+        <v>-1.950147720252211</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.223121048133279</v>
+        <v>-2.231259025256861</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.608701348899068</v>
+        <v>-2.616828620611081</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.550066947451683</v>
+        <v>-2.558256847677256</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.856922364562443</v>
+        <v>-2.864988454227735</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.690897388264823</v>
+        <v>-2.699104800123479</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.822946283445582</v>
+        <v>-2.81465530846765</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.7163</t>
+          <t>X &lt; 0.7162</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.04552557105616</v>
+        <v>-1.052344601962929</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.208096959509824</v>
+        <v>-1.215080686967866</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.980874241577375</v>
+        <v>-0.9880021765247733</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9057720854765776</v>
+        <v>-0.9129148307038903</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8214197203522531</v>
+        <v>-0.8286728576195941</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.8050302962003144</v>
+        <v>-0.8122531537621924</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.24641475735185</v>
+        <v>-1.253487510490878</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.768858742202568</v>
+        <v>-1.775803501907845</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.073768977250069</v>
+        <v>-2.080611623970078</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.488743311406481</v>
+        <v>-2.495551275289067</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.182517056388313</v>
+        <v>-2.189473304277989</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.543112794345106</v>
+        <v>-2.549932648450373</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.338622068552418</v>
+        <v>-2.345581751687654</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.295126869427619</v>
+        <v>-2.288223458487316</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.7488465546831051</v>
+        <v>-0.7543726053512358</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.120718739456954</v>
+        <v>-1.126296122202504</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.938428125804343</v>
+        <v>-0.9441160912502511</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9641088204710471</v>
+        <v>-0.9697768563849749</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7501172058134031</v>
+        <v>-0.7559228986499278</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.062896193817288</v>
+        <v>-1.068563189413439</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.443592250043856</v>
+        <v>-1.449138980102617</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.067035967729957</v>
+        <v>-2.072419814355293</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.214426515937163</v>
+        <v>-2.219768909291176</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.275959087289614</v>
+        <v>-2.281377504033031</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.076721623832512</v>
+        <v>-2.082235866934425</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.373616336654408</v>
+        <v>-2.379026233789382</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.179340322931445</v>
+        <v>-2.184868316309007</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.331131457032029</v>
+        <v>-2.325472592716309</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9921328371812521</v>
+        <v>-0.9964135835523038</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9218581623613034</v>
+        <v>-0.9263057789506632</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.005432566616022</v>
+        <v>-1.009890158696017</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.282401110560905</v>
+        <v>-1.286759403301765</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.9538003562224233</v>
+        <v>-0.9583158989124954</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9002439208388893</v>
+        <v>-0.9047534307091283</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.229022646985044</v>
+        <v>-1.233434757462213</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.874987099788527</v>
+        <v>-1.879231707498128</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.983994990944396</v>
+        <v>-1.988211864942137</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.031095780294478</v>
+        <v>-2.035374734183357</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.956201903174104</v>
+        <v>-1.960526017121147</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.100553694930241</v>
+        <v>-2.104830111332532</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.011586986922389</v>
+        <v>-2.01593224642167</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.235594698643872</v>
+        <v>-2.231010886674525</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3236</v>
+        <v>3237</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.7236630047282802</v>
+        <v>-0.7270698766882049</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.026194199184083</v>
+        <v>-1.029621360286392</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.8503580034911806</v>
+        <v>-0.8538685822448429</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.9192270142489676</v>
+        <v>-0.9227093441304248</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7015772276284054</v>
+        <v>-0.7051658907502585</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7573392136197086</v>
+        <v>-0.760892085451971</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.9488095119678732</v>
+        <v>-0.952311238860311</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.491950180647635</v>
+        <v>-1.495318839474486</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.567244860498583</v>
+        <v>-1.570596485185476</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.598340329808536</v>
+        <v>-1.601743381310897</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.508411558219365</v>
+        <v>-1.511858582638119</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.735062992986997</v>
+        <v>-1.738439650282864</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.675086230392886</v>
+        <v>-1.678512638494439</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.779200130650807</v>
+        <v>-1.775615355563289</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6556320191598033</v>
+        <v>-0.6582271999715061</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.7347172147616305</v>
+        <v>-0.737376335966907</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4134825078385447</v>
+        <v>-0.4162578094912419</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6469997699370396</v>
+        <v>-0.6497014879405754</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5272076007401623</v>
+        <v>-0.5299744142109191</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7105191421009067</v>
+        <v>-0.7132180938329498</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.8671698413596118</v>
+        <v>-0.8698290240034652</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.055537639246516</v>
+        <v>-1.058168139671118</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.071477003130184</v>
+        <v>-1.074107567532224</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.233052306092119</v>
+        <v>-1.235682440622234</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.275476608564844</v>
+        <v>-1.278106745590968</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.57618185458859</v>
+        <v>-1.578723666887839</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.512048925344921</v>
+        <v>-1.514633418889233</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.597568522841875</v>
+        <v>-1.594771280289031</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3601</v>
+        <v>3602</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3628351104700727</v>
+        <v>-0.3647334579202379</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3546659602985116</v>
+        <v>-0.3566289636645905</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6515971403245331</v>
+        <v>-0.6534940453031197</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7556701546293993</v>
+        <v>-0.757534300534509</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5867190823462991</v>
+        <v>-0.5886515705883255</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6898531131427248</v>
+        <v>-0.6917467137102307</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.7596420538985456</v>
+        <v>-0.7615205761145276</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9623575573520995</v>
+        <v>-0.9641987671098562</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.8974006586361156</v>
+        <v>-0.899263223570486</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.011235656943342</v>
+        <v>-1.013100194657909</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.950988311639712</v>
+        <v>-0.9528784281886971</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.289814309447081</v>
+        <v>-1.291610135274503</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.278377025658692</v>
+        <v>-1.280193140485011</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.45759601642488</v>
+        <v>-1.455520642795165</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3754</v>
+        <v>3755</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1706350284658811</v>
+        <v>-0.1719988330821209</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2282195805454421</v>
+        <v>-0.2296120784694295</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5025366822675039</v>
+        <v>-0.5038676666113133</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.7298825549847834</v>
+        <v>-0.731150356796725</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6162602555865391</v>
+        <v>-0.6175734120157017</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.5170395330578401</v>
+        <v>-0.5183717542897739</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5873904884977748</v>
+        <v>-0.5887069960296429</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8540132622757426</v>
+        <v>-0.855272165407591</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7409486337896922</v>
+        <v>-0.7422399414181697</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.7516691953069881</v>
+        <v>-0.7529812742986053</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.8352295518906061</v>
+        <v>-0.8365256303848128</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.9458295753907038</v>
+        <v>-0.947095995630761</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.9518902610191304</v>
+        <v>-0.9531671176197847</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.086901911297801</v>
+        <v>-1.085434782816499</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3862</v>
+        <v>3863</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2611802556938514</v>
+        <v>-0.2621337807923538</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1814187478360836</v>
+        <v>-0.1824247042433385</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4074458347101455</v>
+        <v>-0.4084016446464531</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5473134575765499</v>
+        <v>-0.5482311171531862</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4260027392853445</v>
+        <v>-0.4269627112489758</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4762398594552266</v>
+        <v>-0.4771815580782146</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4952888088481942</v>
+        <v>-0.4962277358637266</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5606624734795105</v>
+        <v>-0.5615941189857949</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4782432074954954</v>
+        <v>-0.4791978502830574</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4864787700249096</v>
+        <v>-0.4874483954627848</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4698641331001241</v>
+        <v>-0.4708425709375064</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.576317275401955</v>
+        <v>-0.5772680143308335</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.6715220023542656</v>
+        <v>-0.672456833784068</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7698087612878837</v>
+        <v>-0.7687563218258404</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3949</v>
+        <v>3950</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.09565942066429045</v>
+        <v>-0.09635887686288669</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2297279139871549</v>
+        <v>-0.2304161064351362</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3332139731041579</v>
+        <v>-0.333881839582709</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.391350164399995</v>
+        <v>-0.3920019001184016</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3602973326447909</v>
+        <v>-0.3609646922985377</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3776019829024406</v>
+        <v>-0.378261210105201</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4739047080610632</v>
+        <v>-0.4745411163316575</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4216895137215246</v>
+        <v>-0.4223459246454055</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.443554135769574</v>
+        <v>-0.4442062108858451</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5209042209616825</v>
+        <v>-0.5215488517182578</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4838678831459546</v>
+        <v>-0.4845250681640323</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.561913342754977</v>
+        <v>-0.5625506557038946</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.588324382612285</v>
+        <v>-0.5889611860119075</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.6282774110938831</v>
+        <v>-0.6275136986923755</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4030</v>
+        <v>4031</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1160101091741481</v>
+        <v>0.1155231386051128</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04761460511880955</v>
+        <v>-0.04807541076117872</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2558816296248168</v>
+        <v>-0.256294587027142</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2112116655791638</v>
+        <v>-0.2116347542724029</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2658105444687138</v>
+        <v>-0.2662250465734175</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2767781564861522</v>
+        <v>-0.2771875574505245</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3480529119977049</v>
+        <v>-0.348445619457955</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3557845546866005</v>
+        <v>-0.3561796512486453</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3536353109194863</v>
+        <v>-0.354031688039008</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.3721120357402157</v>
+        <v>-0.3725115021235723</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3646904190867915</v>
+        <v>-0.3650937381373609</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.366042948279798</v>
+        <v>-0.3664458483002022</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3755116559276317</v>
+        <v>-0.3759161160476907</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.359961846705005</v>
+        <v>-0.3594896194834547</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4075</v>
+        <v>4076</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.04725436717671272</v>
+        <v>-0.04755824134383602</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2268617007298985</v>
+        <v>-0.2271314778056137</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4127538654193756</v>
+        <v>-0.4129806774258924</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3182199184240346</v>
+        <v>-0.3184692164535505</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3781760483863223</v>
+        <v>-0.3784140500514965</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2633131278948042</v>
+        <v>-0.2635776002724839</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2367417756774586</v>
+        <v>-0.2370134098722332</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.249512383788506</v>
+        <v>-0.2497838515919426</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.223523786755905</v>
+        <v>-0.2238021367499314</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.226627643026788</v>
+        <v>-0.2269105107976728</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2460334878620856</v>
+        <v>-0.2463129847398164</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2469624794476672</v>
+        <v>-0.2472416906440174</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2118694317421088</v>
+        <v>-0.2121599402882168</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2427732763203068</v>
+        <v>-0.242450159109012</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volatility/bb_pct_20.xlsx
+++ b/workspaces/btc_daily_14days/volatility/bb_pct_20.xlsx
@@ -568,209 +568,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.06354</t>
+          <t>X ≈ -0.06345</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>36</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.064546631583141</v>
+        <v>3.035474511881354</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.619179236161322</v>
+        <v>-9.620439281580616</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.704513256433749</v>
+        <v>-1.704678473819179</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.19588573239249</v>
+        <v>1.195400836343197</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.430346825872434</v>
+        <v>3.47880531884438</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-12.90552425671926</v>
+        <v>-12.88168352719106</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.901400449388809</v>
+        <v>-1.853481535021771</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.179079984342295</v>
+        <v>3.228266700406124</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3447694419202421</v>
+        <v>0.4179353139414133</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.279225568043955</v>
+        <v>-3.179987483673841</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.035977343946428</v>
+        <v>-8.936163500888469</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.227448537875688</v>
+        <v>-6.10382305213173</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-12.20322624696959</v>
+        <v>-12.0545826617116</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.202759830899268</v>
+        <v>-9.030761071332606</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02138</t>
+          <t>X ≈ -0.02131</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>1.000611533927575</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-13.57500418541714</v>
+        <v>-12.49094381496593</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.223419058544685</v>
+        <v>-10.51986318292852</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.720879338443943</v>
+        <v>-5.637937103650557</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-12.01123972610971</v>
+        <v>-13.26393873574256</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-6.964536204078918</v>
+        <v>-5.863206493792973</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-11.80463563618545</v>
+        <v>-10.67876941632587</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.896630535254253</v>
+        <v>-8.778441026918337</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-12.33779112050594</v>
+        <v>-11.19982075734988</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.675591179648123</v>
+        <v>-2.529947659114526</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-8.639317988653495</v>
+        <v>-8.539505521614821</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.2273877307885</v>
+        <v>-6.103763795141127</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.649000496021863</v>
+        <v>-6.500354156955744</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293557172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.02077</t>
+          <t>X ≈ 0.02084</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>78</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.360394790181495</v>
+        <v>1.331640540190335</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.424235758513333</v>
+        <v>7.424914282323648</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13.42442732432097</v>
+        <v>13.42779603958557</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.327259607117064</v>
+        <v>3.327599309550379</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2325247795433967</v>
+        <v>0.2810800183655857</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.926955693048519</v>
+        <v>6.952621791218476</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.004711357538106</v>
+        <v>3.053401140957376</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.099179175888793</v>
+        <v>5.149678718671574</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.198527874813635</v>
+        <v>1.271979096739841</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3497186646166597</v>
+        <v>0.4490523591269877</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.541055986344887</v>
+        <v>-7.44124464747641</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-6.22729046043834</v>
+        <v>-6.103669014549361</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.803775007166998</v>
+        <v>-2.65512738964442</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.142930771072052</v>
+        <v>-4.970932011504814</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.06293</t>
+          <t>X ≈ 0.06298</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>91</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>12.31200973178048</v>
+        <v>12.24069839528999</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.041390632585866</v>
+        <v>2.951869275422233</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.839380474616128</v>
+        <v>5.844937961939131</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.355102310830411</v>
+        <v>9.267320964587064</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.91668925248414</v>
+        <v>9.86860091018405</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.022951553597565</v>
+        <v>8.550092523679147</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.552924788480027</v>
+        <v>4.101160228228487</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.087331544054031</v>
+        <v>3.632987415803235</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.027579341533844</v>
+        <v>3.594270267203406</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.113966720097316</v>
+        <v>-1.015018835079211</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.514644441829468</v>
+        <v>-3.414829076024446</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.382999991431788</v>
+        <v>-2.259376517288501</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.705126019347951</v>
+        <v>-1.556479524708109</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.479927108067308</v>
+        <v>-1.307928348501143</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>100</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.480720715371632</v>
+        <v>-0.5514152386554301</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.901721323959173</v>
+        <v>1.821930144910176</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4863067191381205</v>
+        <v>-0.5702780002953105</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.6409516108799238</v>
+        <v>1.558539884910061</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.087147956520248</v>
+        <v>8.054165690880133</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.583937150998679</v>
+        <v>-5.654158034671084</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.675600182564196</v>
+        <v>-2.721924774189809</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.138234049129331</v>
+        <v>-6.643363192337567</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-11.19530565292999</v>
+        <v>-11.12816075702937</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-13.04615971605969</v>
+        <v>-12.95045788167603</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.260336661058112</v>
+        <v>-5.16053061019327</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.228091872142279</v>
+        <v>-4.104475253337547</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.648559631403927</v>
+        <v>-7.499920102230824</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.424982053123209</v>
+        <v>-6.252983293555637</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.314905260403322</v>
+        <v>-2.13819076152847</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.692427511394889</v>
+        <v>-4.501446727424359</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.322156962078324</v>
+        <v>0.4796594168875217</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.185780548109598</v>
+        <v>-3.999559670012957</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.950911935061661</v>
+        <v>-2.954392355850366</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.333394542315034</v>
+        <v>-0.3769293383430963</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4179440777205201</v>
+        <v>-1.207138917269269</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.980000428364903</v>
+        <v>-3.213821636790591</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.719139501388106</v>
+        <v>-0.9472388025574787</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.117200378829608</v>
+        <v>-3.315538834149571</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.548291928715777</v>
+        <v>-2.753733515459956</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.289915593412864</v>
+        <v>-3.796800813920434</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.261210829492462</v>
+        <v>-5.731045017991434</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-6.812578952347913</v>
+        <v>-7.022214062787214</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.275666550262436</v>
+        <v>4.286077574180361</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7442266949592877</v>
+        <v>0.7487610436317951</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.278936148899824</v>
+        <v>2.949682971134692</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.410044841904039</v>
+        <v>3.080429148618315</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.873192282443128</v>
+        <v>1.941913540858316</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.171466059807265</v>
+        <v>2.214208217010516</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.775462773508693</v>
+        <v>-1.38672907966717</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.242052108728551</v>
+        <v>-2.501232688930934</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.303206149642108</v>
+        <v>-2.538013148898251</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5750097027006262</v>
+        <v>-0.7653329170827661</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.154076119953906</v>
+        <v>0.9776760646075147</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.188494093326874</v>
+        <v>1.035762739818658</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.70358617277261</v>
+        <v>2.588370068017177</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.639534075909793</v>
+        <v>1.53922449865199</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>138</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.308155029025734</v>
+        <v>0.01121306079813422</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.420960894861302</v>
+        <v>2.757463669077005</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.304343004878504</v>
+        <v>1.641373490949249</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.880142053632461</v>
+        <v>3.220192011196673</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.992467361442898</v>
+        <v>-1.947009116908049</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9723912377638584</v>
+        <v>-0.9499701833943277</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.056703897039</v>
+        <v>-1.010452065089773</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.7997085634138443</v>
+        <v>-0.7517352579772449</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.757276296454322</v>
+        <v>2.832506944100501</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.185487499205159</v>
+        <v>1.285069516451472</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.638679219181022</v>
+        <v>-2.53988506498068</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.605403913617785</v>
+        <v>-2.481805431380714</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.026378839671217</v>
+        <v>-2.877748162311001</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.6278806038473874</v>
+        <v>-0.4558818442807251</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.23088468033955</v>
+        <v>2.191338307171002</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.332615187954552</v>
+        <v>5.311650859194529</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.939761721839965</v>
+        <v>4.919518297454701</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.30169868978966</v>
+        <v>3.287527701843757</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.943441294651144</v>
+        <v>3.974289045406849</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.061145451653211</v>
+        <v>3.071389189674385</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.747934536789366</v>
+        <v>4.774509775777723</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1443700526774236</v>
+        <v>0.1940076938504518</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.628076510631573</v>
+        <v>3.684339821869756</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.364194685497992</v>
+        <v>-1.253852094641175</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9806732245458392</v>
+        <v>-0.8698247449377519</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.720726081283082</v>
+        <v>-2.575339062324076</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.737035255204717</v>
+        <v>-3.559436750147782</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.395396254306185</v>
+        <v>-1.547100940614911</v>
       </c>
     </row>
     <row r="15">
@@ -1040,153 +1040,153 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.270071074277638</v>
+        <v>-3.027093314776771</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-5.410401201497884</v>
+        <v>-5.128488926048512</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-8.954991184523216</v>
+        <v>-8.645785048236746</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-9.352609735960982</v>
+        <v>-9.038983601103183</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.694541410248213</v>
+        <v>-5.364104255411455</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.874066105273116</v>
+        <v>-4.570751697516364</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.537457371557849</v>
+        <v>-6.192701078004617</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.279566371285064</v>
+        <v>-1.973645131947777</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.918955505732725</v>
+        <v>-3.572039819494485</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.828406565537833</v>
+        <v>-5.435929252236171</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.933068437700499</v>
+        <v>-3.557823007992077</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.426438817306462</v>
+        <v>-4.02018038065448</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.91387559808625</v>
+        <v>-1.81353057518966</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.898666263649069</v>
+        <v>-5.732149960222756</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.3579</t>
+          <t>X ≈ 0.358</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-7.738284880384093</v>
+        <v>-7.981527453280663</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-8.109165392527245</v>
+        <v>-8.581768059481043</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-11.50013497473102</v>
+        <v>-11.96187827305418</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-9.878175423942146</v>
+        <v>-10.34460894719718</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.92973582790848</v>
+        <v>-6.358650148556869</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.139024717845643</v>
+        <v>-3.599672633205977</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.453102986889618</v>
+        <v>-3.164555450241238</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.422940370982815</v>
+        <v>-4.130369826658793</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.486701253093685</v>
+        <v>-3.17330205802584</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.845251890200274</v>
+        <v>-2.511992926485483</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.05283920381555873</v>
+        <v>-0.2311882941844559</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.269433149964122</v>
+        <v>2.81112581611832</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.349282296650713</v>
+        <v>3.696116832487206</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.075017946877132</v>
+        <v>0.4634346168917745</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.4001</t>
+          <t>X ≈ 0.4002</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.484019908730474</v>
+        <v>-5.945823647960673</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.223575939292409</v>
+        <v>-5.2583445354418</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.327029583989116</v>
+        <v>-3.371168080900993</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.388765901805989</v>
+        <v>1.071251276192399</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2966786485853703</v>
+        <v>-0.5604684445551555</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.869606739434396</v>
+        <v>2.56832482416236</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.211582879279277</v>
+        <v>2.507795259629631</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.320015746300285</v>
+        <v>2.613422721931236</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.111207692322353</v>
+        <v>1.434063882794092</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.411008020533558</v>
+        <v>1.753226038845241</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.378733158528334</v>
+        <v>6.690034500798859</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.390122805136407</v>
+        <v>2.749652616973584</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.544684595501288</v>
+        <v>2.354649331701268</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6778556163410201</v>
+        <v>-0.8244118649847962</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.417713411055857</v>
+        <v>3.042085580606233</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.012612305993095</v>
+        <v>-1.622000669090433</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.355160657522312</v>
+        <v>1.685431071491266</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.093820928901081</v>
+        <v>3.049244516510917</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.469708212210698</v>
+        <v>-2.376266811330332</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.824367549361327</v>
+        <v>-2.103593410208298</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.798863296586653</v>
+        <v>-4.632220424740467</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.694216647987986</v>
+        <v>-8.799953514235327</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.873648700499707</v>
+        <v>-6.985775748643874</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.333431851702613</v>
+        <v>-3.48977828961592</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.321548775976105</v>
+        <v>-6.779110633382139</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.916101441230843</v>
+        <v>-7.337972665175002</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-6.336252294544252</v>
+        <v>-7.115925637629324</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.852655009097596</v>
+        <v>-5.635699342938807</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.932159607513405</v>
+        <v>-6.863249845395508</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.139071638850162</v>
+        <v>-3.082842386181959</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.895428685955444</v>
+        <v>-4.820164035678914</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.399816961097265</v>
+        <v>-3.348771540751194</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.263213651819804</v>
+        <v>-3.167066131780473</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.002715605511632</v>
+        <v>-4.906943939663577</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-8.496104289231205</v>
+        <v>-8.321589697425566</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-6.255031339599363</v>
+        <v>-6.103622469305371</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-10.01530995567168</v>
+        <v>-10.16564856402819</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.482012551614</v>
+        <v>-10.98889438683191</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-10.68671370987419</v>
+        <v>-11.19299841199223</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-10.65233555751887</v>
+        <v>-11.13481346343953</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.310581648927517</v>
+        <v>-6.833872298554724</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.765118107544524</v>
+        <v>-7.259694702952061</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.485441126860934</v>
+        <v>-6.123389120498892</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.594360582223295</v>
+        <v>-1.254086401086845</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-6.33886729991054</v>
+        <v>-6.282139329613123</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-6.204809784275767</v>
+        <v>-6.152503357080285</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.445662555541716</v>
+        <v>-3.765301692215893</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.423650844747037</v>
+        <v>-2.773512001991243</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-7.580824972129477</v>
+        <v>-7.867404014958417</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-6.59861825359738</v>
+        <v>-6.894670277995878</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.108875772438829</v>
+        <v>-8.369671902334687</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-6.316491522798749</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.815669640072365</v>
+        <v>-5.08241690362172</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.679842212354721</v>
+        <v>-7.900576937731977</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.27390610914655</v>
+        <v>-10.45293343002454</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.874257415441598</v>
+        <v>-8.051544444635226</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>145</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.574315600106509</v>
+        <v>-4.600812590373479</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.441767975796324</v>
+        <v>-3.44295476224098</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.142045922146323</v>
+        <v>-4.528613331794865</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-8.839406985454353</v>
+        <v>-9.222431939490569</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-6.61907584889488</v>
+        <v>-6.953384020619225</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.011356991673743</v>
+        <v>-7.368635525053307</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.337446661284581</v>
+        <v>-4.678761670428614</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.114860132657526</v>
+        <v>-4.46044096554543</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.727566427111654</v>
+        <v>-1.052050381103236</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.577485223441357</v>
+        <v>-1.884940597219419</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9764343079536317</v>
+        <v>0.6695396448996576</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.43746340176002</v>
+        <v>-2.722187628965663</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5906616069957025</v>
+        <v>0.3289885275463078</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.264673119290883</v>
+        <v>4.436671878857545</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>151</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.798796825236487</v>
+        <v>-4.523210135578388</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4497180176380624</v>
+        <v>-0.4509048040827182</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5.115775498269301</v>
+        <v>5.115622108264979</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.934742363711962</v>
+        <v>1.934247871333959</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.577057123158568</v>
+        <v>-2.528511203392796</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2929281266360633</v>
+        <v>-0.2689707176864502</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.026645108418791</v>
+        <v>-2.97863342942847</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1824554740598288</v>
+        <v>-0.133207911666112</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.230192597469873</v>
+        <v>-2.156935487690177</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.093356426912464</v>
+        <v>-0.9940091016178911</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.947064207689216</v>
+        <v>-3.847156171670541</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.912686055333893</v>
+        <v>-3.788989434305648</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.332836908647302</v>
+        <v>-4.184147360869474</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.769352914049911</v>
+        <v>-4.597354154483249</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>153</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1933343311879412</v>
+        <v>-0.2225301255405725</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.458115195493598</v>
+        <v>-2.459301981938253</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.2385074952812474</v>
+        <v>-0.2386608852855687</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.722661436660275</v>
+        <v>-2.723155929038278</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.260950989756125</v>
+        <v>-3.212405069990353</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.577956045088214</v>
+        <v>-5.553998636138601</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.087503005661567</v>
+        <v>-1.039491326671246</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4062126642771844</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.9619590347291762</v>
+        <v>-0.8887019249494799</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.158283059817279</v>
+        <v>-1.058935734522706</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.670173760561056</v>
+        <v>-2.570265724542381</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6750112944803206</v>
+        <v>-0.551314673452076</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.402351690277314</v>
+        <v>-2.253662142499486</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.830210811292538</v>
+        <v>-2.658212051725876</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>168</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.836469304973249</v>
+        <v>4.835282518528594</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.25122172974195</v>
+        <v>3.251068339737628</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.548113539997047</v>
+        <v>7.547619047619044</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.224109701187061</v>
+        <v>5.272655620952833</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.116721826060243</v>
+        <v>6.140679235009856</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.412963847746461</v>
+        <v>8.460975526736782</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>0.8522856234963001</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.1468178093416412</v>
+        <v>0.2200749191213376</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.7031009869881473</v>
+        <v>-0.6037536616935739</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.258864521418253</v>
+        <v>3.358772557436929</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.873091820460168</v>
+        <v>3.021781368237995</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.479779851639151</v>
+        <v>5.651778611205813</v>
       </c>
     </row>
     <row r="25">
@@ -1563,98 +1563,98 @@
         <v>207</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.074639525021148</v>
+        <v>3.045443730668516</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.01417806963853252</v>
+        <v>0.01299128319387677</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3805933151165064</v>
+        <v>-0.3807467051208278</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.699643533846981</v>
+        <v>-1.700138026224984</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1775258502553925</v>
+        <v>0.2260717700211643</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.356017994505656</v>
+        <v>-4.332060585556043</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.957636566332212</v>
+        <v>-3.909624887341892</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-5.873980572437787</v>
+        <v>-5.824733010044071</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.002595579202108</v>
+        <v>-3.929338469422412</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4614952863037729</v>
+        <v>0.5608426115983463</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-0.6094814108169686</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.1919195070407014</v>
+        <v>-0.06822288601245674</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1289785729145052</v>
+        <v>0.01971097486332241</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.801793647325646</v>
+        <v>-2.629794887758983</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.7795</t>
+          <t>X ≈ 0.7794</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>198</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-4.501118050736316</v>
+        <v>-4.530313845088948</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.968503937007874</v>
+        <v>1.967317150563218</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.961620983100758</v>
+        <v>-1.961774373105079</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-5.871799879916374</v>
+        <v>-5.872294372294377</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.884836907759478</v>
+        <v>-3.836290987993706</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.463042172380533</v>
+        <v>1.486999581330146</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.883382318164927</v>
+        <v>1.931393997155247</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.9112631693276825</v>
+        <v>0.9605107317213992</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.355331517855412</v>
+        <v>1.428588627635108</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.515513731626505</v>
+        <v>1.614861056921079</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2043389417852026</v>
+        <v>-0.1044309057665274</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.850241230772198</v>
+        <v>1.973937851800443</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.4199893673577861</v>
+        <v>0.5686789151356137</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.735300185681865</v>
+        <v>4.011627305547798</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.740750772246834</v>
+        <v>-2.462854127434149</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.729342707863054</v>
+        <v>2.034712232077304</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.102811094694601</v>
+        <v>5.425465838509311</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.483440460517762</v>
+        <v>3.849260175818202</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.618652327990809</v>
+        <v>1.948132651158993</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.696104130886681</v>
+        <v>4.061389605411733</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>5.225991627637086</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.330215492739399</v>
+        <v>5.732497279369909</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.561377777490669</v>
+        <v>5.995625220294066</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.897217159771081</v>
+        <v>6.334963033627538</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.30997369050467</v>
+        <v>4.762694988383679</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.889822837191261</v>
+        <v>4.367537061819853</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.737180109039407</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="28">
@@ -1716,205 +1716,205 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.5917096677896723</v>
+        <v>0.2676659528907948</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.567115753496758</v>
+        <v>4.240044423290463</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.524299676004297</v>
+        <v>7.179639768309094</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.302569512330116</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.646961523480229</v>
+        <v>2.375830224127441</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1510394637298376</v>
+        <v>-0.1291620348314098</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.6249883223408261</v>
+        <v>0.3657374314986939</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.861830293079166</v>
+        <v>6.566571337782015</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.918166572310575</v>
+        <v>7.640709839756255</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.392270122349437</v>
+        <v>5.150214592274679</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.952932092580802</v>
+        <v>2.723851922516367</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.311332591304904</v>
+        <v>1.115351993214588</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.449840955868595</v>
+        <v>1.275749622206312</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.675576606095127</v>
+        <v>1.52479448422168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.906</t>
+          <t>X ≈ 0.9059</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>186</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.045965689895759</v>
+        <v>5.016769895543128</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.660586048444863</v>
+        <v>6.659399262000207</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.024507916955343</v>
+        <v>-5.024661306959665</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.743745138958374</v>
+        <v>-2.744239631336377</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.669131466247656</v>
+        <v>-1.620585546481884</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2964886194082297</v>
+        <v>-0.2725312104586166</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.231704247132015</v>
+        <v>1.279715926122336</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.7646356033452761</v>
+        <v>0.8138831657389929</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.316556672628963</v>
+        <v>2.389813782408659</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.079541102105551</v>
+        <v>3.178888427400125</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.025377578253959</v>
+        <v>5.125285614272634</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.98448691340495</v>
+        <v>4.108183534433195</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.026701651489425</v>
+        <v>3.175391199267253</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.101899667307357</v>
+        <v>1.27389842687402</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.9481</t>
+          <t>X ≈ 0.948</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.38182906750486</v>
+        <v>4.726730280376167</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.770642974441031</v>
+        <v>3.143553195220306</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.029466360927842</v>
+        <v>3.407709943747726</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1082823516929992</v>
+        <v>0.2481203007518431</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.300166676030486</v>
+        <v>-0.8990235770421506</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.572370752297367</v>
+        <v>3.979025099671482</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.487660393031248</v>
+        <v>3.260474273603954</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.713402206760804</v>
+        <v>1.478852039536392</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.959609592721733</v>
+        <v>2.757668904083815</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.37766465260102</v>
+        <v>5.223314007479352</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.90498963813171</v>
+        <v>1.72969987573277</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.168125960421683</v>
+        <v>7.051024507834512</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.747975107108275</v>
+        <v>6.655866581270644</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.627305528576592</v>
+        <v>7.562806180128121</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.9901</t>
+          <t>X ≈ 0.99</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.406841956460276</v>
+        <v>-3.886258613877807</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.463453431957376</v>
+        <v>0.9525826495902194</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.920533899054163</v>
+        <v>2.393707046596589</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.828536820420325</v>
+        <v>5.275884665792915</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.216173193250562</v>
+        <v>5.704066717501554</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.4722650803571753</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.72513315991575</v>
+        <v>3.16390256911334</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.665471923536494</v>
+        <v>10.03751935001443</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.678563841087737</v>
+        <v>9.083115548217087</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.754570970683801</v>
+        <v>9.176718160062649</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.25357351612726</v>
+        <v>12.64230248316871</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.28795166848264</v>
+        <v>12.70046922053366</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.090023037391418</v>
+        <v>9.553017715988197</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.24168461354389</v>
+        <v>10.71949377066407</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>87</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.289198911994369</v>
+        <v>7.260003117641737</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.367964192563697</v>
+        <v>-2.369150979008353</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.98439085946287</v>
+        <v>2.984237469458549</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.5628918651202</v>
+        <v>6.562397372742197</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.576326449955538</v>
+        <v>2.624872369721309</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.02312576694694</v>
+        <v>4.047083175896553</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.4901395456118465</v>
+        <v>0.5381512246021671</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.770197338606657</v>
+        <v>5.819444901000374</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.111514032658619</v>
+        <v>1.184771142438315</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.037255338383879</v>
+        <v>-1.937908013089306</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.092531209287756</v>
+        <v>-0.9926231732690809</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.09127223042388977</v>
+        <v>0.2149688514521344</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.119397239179456</v>
+        <v>3.268086786957284</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.643983464118691</v>
+        <v>5.815982223685353</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>81</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>10.48204693242862</v>
+        <v>10.45285113807599</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8.870860839364759</v>
+        <v>8.869674052920104</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.537817849671477</v>
+        <v>3.537664459667155</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.606314598198104</v>
+        <v>8.605820105820101</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.364321341398693</v>
+        <v>4.412867261164465</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.661695371033787</v>
+        <v>4.6856527799834</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.811552913002195</v>
+        <v>5.859564591992516</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.875348466746352</v>
+        <v>2.924596029140069</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.048934211458104</v>
+        <v>4.1221913212378</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.902719118831953</v>
+        <v>7.002066444126527</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.463450059337191</v>
+        <v>5.563358095355866</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.201531915396224</v>
+        <v>9.325228536424468</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>10.01594896331734</v>
+        <v>10.16463851109517</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>12.71082041601301</v>
+        <v>12.88281917557968</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>45</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-14.70313825275657</v>
+        <v>-14.73233404710921</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-16.31432434582037</v>
+        <v>-16.31551113226503</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-14.48687350835322</v>
+        <v>-14.48702689835754</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.912203920320415</v>
+        <v>-9.912698412698418</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.45049347341607</v>
+        <v>-10.4019475536503</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.9579916673301057</v>
+        <v>0.9819490762797187</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.762170196952823</v>
+        <v>9.810181875943144</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.295101553166084</v>
+        <v>9.344349115559801</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.45634161886554</v>
+        <v>11.52959872864523</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.82864504475788</v>
+        <v>12.92799237005245</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.46039340776183</v>
+        <v>14.60908295553966</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
   </sheetData>
@@ -2210,313 +2210,313 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.08461</t>
+          <t>X &gt; -0.08453</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4076</v>
+        <v>4087</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.07201409852163465</v>
+        <v>-0.07108743464308276</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.03143676156295783</v>
+        <v>-0.03132257679082784</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02149548045990457</v>
+        <v>-0.02143392617598749</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.02478346021273126</v>
+        <v>-0.02470448760417554</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1825756167589603</v>
+        <v>-0.1833060605947807</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.09217701261331968</v>
+        <v>-0.09253199820137326</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.114554433629273</v>
+        <v>-0.1154545567768395</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1272948755997803</v>
+        <v>-0.1281920794343705</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02777175204030868</v>
+        <v>-0.02954105630102788</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.006322275503556796</v>
+        <v>-0.008806565279854794</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.04787676765047877</v>
+        <v>0.04523198228273628</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.07154202686455591</v>
+        <v>0.06823370838537102</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1067019679776706</v>
+        <v>0.102668517618369</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.0274222648360265</v>
+        <v>0.02301377030493512</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.04246</t>
+          <t>X &gt; -0.04238</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4040</v>
+        <v>4051</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.09869450205233932</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.05399856741860276</v>
+        <v>0.05389297526359371</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.00649829235717192</v>
+        <v>-0.006475445871082286</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.03566071044387087</v>
+        <v>-0.03554719105076742</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2147699751586458</v>
+        <v>-0.2158501261735992</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.02200132916584607</v>
+        <v>0.02112128618362163</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.09863204338983422</v>
+        <v>-0.1000092417393645</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.156757621876487</v>
+        <v>-0.1580199036936278</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.03109142604589721</v>
+        <v>-0.03351764216346709</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.02284220928145686</v>
+        <v>0.01937475120055865</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1288220023082758</v>
+        <v>0.1250469014123752</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1276716457582907</v>
+        <v>0.1230828921371909</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2163943976158222</v>
+        <v>0.2107062965509456</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1096714122237756</v>
+        <v>0.1034719026917514</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003048</t>
+          <t>X &gt; -0.0002374</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3998</v>
+        <v>4009</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.1102113026288336</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1971746843818636</v>
+        <v>0.1853180551312903</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.09032778872834513</v>
+        <v>0.103667304180405</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03456920010540898</v>
+        <v>0.0231458437033325</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.09084508032623972</v>
+        <v>-0.07915276483613098</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.09539667093579851</v>
+        <v>0.08276802271618067</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.02434248159701013</v>
+        <v>0.01081837794949791</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.0544377963732714</v>
+        <v>-0.06770868214823622</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.09819356324057793</v>
+        <v>0.08346532886118041</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.06169518635375226</v>
+        <v>0.04608254397513178</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2209335279762072</v>
+        <v>0.2158204613443218</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1944331499641265</v>
+        <v>0.1883180033533733</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2885171053528879</v>
+        <v>0.2810142384435039</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1783195977026537</v>
+        <v>0.1700648481251292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.04185</t>
+          <t>X &gt; 0.04191</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3920</v>
+        <v>3931</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1290218022099197</v>
+        <v>-0.138820929629567</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.05337091811087902</v>
+        <v>0.0416679646400695</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1749935795819226</v>
+        <v>-0.1607137798596909</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.03094861921778147</v>
+        <v>-0.04242204496012647</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.09727948059916258</v>
+        <v>-0.08630060434001763</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.04053741164705826</v>
+        <v>-0.05354553463390488</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.0349607766487523</v>
+        <v>-0.04955339908296708</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1569842565356296</v>
+        <v>-0.1712335402667691</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.07629915602050374</v>
+        <v>0.05988250670535678</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.05596410693933507</v>
+        <v>0.03808670434607109</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.3753812785162722</v>
+        <v>0.3677540859914785</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3222123442527476</v>
+        <v>0.3131653672293382</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3500474075918021</v>
+        <v>0.3392739807459364</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.2842016203466358</v>
+        <v>0.2720739437881008</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.084</t>
+          <t>X &gt; 0.08405</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3829</v>
+        <v>3840</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4246953121585051</v>
+        <v>-0.4321897469649016</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.01764234749821014</v>
+        <v>-0.02729774350607528</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2941651750198915</v>
+        <v>-0.3030352143658561</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2540174713030225</v>
+        <v>-0.263043558988457</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3352714248954669</v>
+        <v>-0.3222110308560886</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2321742609124584</v>
+        <v>-0.2574338323699692</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1202304518711941</v>
+        <v>-0.1479166647301895</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2340886539902343</v>
+        <v>-0.2613856514653037</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.006159041922380482</v>
+        <v>-0.0238751199106062</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.08376867869706217</v>
+        <v>0.0630431116605763</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4678316155628721</v>
+        <v>0.4573934265496717</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.386504410731547</v>
+        <v>0.3741292504301512</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3988906517421</v>
+        <v>0.3841993893387254</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.3261278972559296</v>
+        <v>0.3095167064439153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.1261</t>
+          <t>X &gt; 0.1262</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3729</v>
+        <v>3740</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4231928878299129</v>
+        <v>-0.4290018995934943</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.06911361785105186</v>
+        <v>-0.07674233945302689</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2890125457863704</v>
+        <v>-0.2958896853303088</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2780177148584713</v>
+        <v>-0.3117489986648891</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5343172651050665</v>
+        <v>-0.5461783228811115</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.06184004557092493</v>
+        <v>-0.1131363938057746</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.02488666719184351</v>
+        <v>-0.07909291848795874</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.04894128485267402</v>
+        <v>-0.0907445407467975</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3065469393440097</v>
+        <v>0.2730309131674318</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4358718804872623</v>
+        <v>0.4109976836749141</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.6214429933215513</v>
+        <v>0.6076052991898564</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5102533054184164</v>
+        <v>0.4938780339533508</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6146978462485677</v>
+        <v>0.5950047233379223</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5071713392076305</v>
+        <v>0.4849846208824076</v>
       </c>
     </row>
     <row r="12">
@@ -2526,101 +2526,101 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3600</v>
+        <v>3610</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3912398611460333</v>
+        <v>-0.367452162183092</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.06072179666760036</v>
+        <v>0.08259604570937285</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3467461198181923</v>
+        <v>-0.3238180463520095</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1738228800003156</v>
+        <v>-0.1789469523282534</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4477226227649567</v>
+        <v>-0.4594559338822179</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.1036369248889173</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.01080210998123476</v>
+        <v>-0.03847076340718303</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.09192166778984046</v>
+        <v>0.02172083944314096</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3791340368035705</v>
+        <v>0.3169741439276095</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5990236364461268</v>
+        <v>0.5451942895799533</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7708584946945578</v>
+        <v>0.728650741268666</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.6822593576265348</v>
+        <v>0.6483900146247024</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.8610845737959565</v>
+        <v>0.8228126087597474</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7694623913216958</v>
+        <v>0.7553269557513929</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.2104</t>
+          <t>X &gt; 0.2105</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3445</v>
+        <v>3456</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.6012167824140491</v>
+        <v>-0.5748143090002173</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.02996903636710613</v>
+        <v>0.05291161003806621</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4648827676124725</v>
+        <v>-0.4696858578951151</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2900781766317166</v>
+        <v>-0.3241853549746025</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5521469508657617</v>
+        <v>-0.5664614023747063</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1521540996358368</v>
+        <v>-0.2069205336425313</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.06859481392204003</v>
+        <v>0.02160787684282184</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1969335503327585</v>
+        <v>0.1341441158811065</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4998198797350852</v>
+        <v>0.4441929063972836</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6518466168721773</v>
+        <v>0.6035916245990762</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7536164825275904</v>
+        <v>0.7175541267448793</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.6594824682118698</v>
+        <v>0.6311286142543722</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7781853726808947</v>
+        <v>0.744139041420155</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7303154795332674</v>
+        <v>0.7203963360735344</v>
       </c>
     </row>
     <row r="14">
@@ -2630,101 +2630,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3307</v>
+        <v>3318</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6134461510162836</v>
+        <v>-0.599187960908651</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.06980625134750085</v>
+        <v>-0.0595742803017103</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5387119652549686</v>
+        <v>-0.557487602964585</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4223704027509925</v>
+        <v>-0.4716006884681647</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4920428635782912</v>
+        <v>-0.5090426005044222</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1179258791756936</v>
+        <v>-0.1760161178300734</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1155531514220698</v>
+        <v>0.06453261222157636</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2385230912148373</v>
+        <v>0.170989008464737</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4056169811843588</v>
+        <v>0.3448597728219198</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6295779619698649</v>
+        <v>0.5752480594768201</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8951758435302466</v>
+        <v>0.8530353227841019</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.7957250810611285</v>
+        <v>0.7605996505104429</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.9369485602541019</v>
+        <v>0.8947781113764179</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.7869925462119909</v>
+        <v>0.7693192983667529</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.2947</t>
+          <t>X &gt; 0.2948</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3138</v>
+        <v>3148</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7666303162486372</v>
+        <v>-0.7498834709383644</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3607588400160893</v>
+        <v>-0.3496340877078055</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.8337604206785088</v>
+        <v>-0.8532598402807423</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6229337158929127</v>
+        <v>-0.6746031746031775</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7309201174791156</v>
+        <v>-0.7511539028566858</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2891378150935111</v>
+        <v>-0.3513842570536241</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1339281915119841</v>
+        <v>-0.1898181240568704</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.243593793417773</v>
+        <v>0.1697459409566093</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2320683322115826</v>
+        <v>0.1645193635658444</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7369545003452771</v>
+        <v>0.6740241160842046</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9962014944240849</v>
+        <v>0.9460741447385885</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.9851069314231893</v>
+        <v>0.9407488186114108</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.188670441966195</v>
+        <v>1.135317033377412</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9045271884323753</v>
+        <v>0.8944118779813905</v>
       </c>
     </row>
     <row r="16">
@@ -2734,101 +2734,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2948</v>
+        <v>2956</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6052823705140682</v>
+        <v>-0.6019726827052878</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.03530699175233565</v>
+        <v>-0.03923485598878074</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3103432411905516</v>
+        <v>-0.3471147658803559</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.06030195069178745</v>
+        <v>-0.1313145948034489</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4110123679451476</v>
+        <v>-0.4515306052617873</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.006362990582928774</v>
+        <v>-0.07732520814671062</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2787823051666791</v>
+        <v>0.2000849636149766</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4062126642771844</v>
+        <v>0.3089648469098023</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4996037898809931</v>
+        <v>0.4072187421678635</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.160095138919836</v>
+        <v>1.070881709696359</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.313895282451114</v>
+        <v>1.238614149246132</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.333883624862352</v>
+        <v>1.262974260512316</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.388631007641216</v>
+        <v>1.326852466680826</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.342996237243597</v>
+        <v>1.324824554887748</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.379</t>
+          <t>X &gt; 0.3791</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2748</v>
+        <v>2755</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.08614099424988098</v>
+        <v>-0.06357322394460851</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5523100679838251</v>
+        <v>0.5840134829955943</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5040520814834366</v>
+        <v>0.5002781433544641</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6542448814225068</v>
+        <v>0.6138295666597529</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.009358549898330182</v>
+        <v>-0.02055745527910346</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2352849489838391</v>
+        <v>0.1796591230463562</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4776094734386049</v>
+        <v>0.4455632660415034</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.6848992025057115</v>
+        <v>0.6328509700993763</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.7169476794715735</v>
+        <v>0.6684473014560481</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.378824908142548</v>
+        <v>1.332282000757175</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.413366496880997</v>
+        <v>1.345848374701497</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.193013935990315</v>
+        <v>1.15002382033925</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.173154203492054</v>
+        <v>1.1539950664895</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.362499751826306</v>
+        <v>1.387670063975662</v>
       </c>
     </row>
     <row r="18">
@@ -2838,101 +2838,101 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2574</v>
+        <v>2580</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3463496549807488</v>
+        <v>0.3354166303975674</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.9427545766342007</v>
+        <v>0.9802974571144105</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7630296299652599</v>
+        <v>0.7628762399609386</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6045919453126629</v>
+        <v>0.5828029003154924</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.01006402087539016</v>
+        <v>0.01606441414853776</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.05720725219347145</v>
+        <v>0.01763722471484641</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3603944879622034</v>
+        <v>0.3056831889570404</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5743668487293903</v>
+        <v>0.4985098629014786</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6902960702112679</v>
+        <v>0.6165159441947452</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.376649359752491</v>
+        <v>1.303729595072902</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.077712340266146</v>
+        <v>0.983355129714262</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.112090492621469</v>
+        <v>1.041521867079155</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.08044002780845</v>
+        <v>1.072555339198011</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.50042587228517</v>
+        <v>1.537714380862511</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.4633</t>
+          <t>X &gt; 0.4634</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1441356437112091</v>
+        <v>0.154076527033709</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.137331526670529</v>
+        <v>1.15464497425468</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7240446057907022</v>
+        <v>0.7010673554663498</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.4407048196851022</v>
+        <v>0.4175574322329183</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1733285281468966</v>
+        <v>0.176344669949863</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1810873322958457</v>
+        <v>0.1597544136551079</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6342338203610751</v>
+        <v>0.6365104782122017</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.118758060314505</v>
+        <v>1.121483836059532</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.122456409152491</v>
+        <v>1.125850623367555</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.620915576158843</v>
+        <v>1.624882728786545</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.499030152888302</v>
+        <v>1.503421074140078</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.574816172738451</v>
+        <v>1.60292720794979</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.568743994373278</v>
+        <v>1.621163245834076</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.918703247084281</v>
+        <v>2.018315300323145</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6027844099942854</v>
+        <v>0.6148881751130162</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.414505805917237</v>
+        <v>1.432911001890233</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.088269726552021</v>
+        <v>1.063633894594005</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6896275276987751</v>
+        <v>0.6648835745751995</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3960673731447386</v>
+        <v>0.3958987508039016</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.5170745597463196</v>
+        <v>0.4924728158783296</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.226014994130942</v>
+        <v>1.224768268503098</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.596688854753374</v>
+        <v>1.595939913406099</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.844348673539237</v>
+        <v>1.867337348322152</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.40536462147746</v>
+        <v>2.453200397463128</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.288846884734014</v>
+        <v>2.33716567679928</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.367316747847717</v>
+        <v>2.439385277600294</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.079441026809448</v>
+        <v>2.17638594134484</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.481543520069479</v>
+        <v>2.62758083160918</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>2130</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.06202155745251</v>
+        <v>1.054616130084874</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.60944644514889</v>
+        <v>1.608259658704235</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.569464519815796</v>
+        <v>1.54300595007043</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.136309381714021</v>
+        <v>1.109774083260703</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6449681854258316</v>
+        <v>0.6674512679774907</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7076004310233586</v>
+        <v>0.7056051584529115</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.79659899194499</v>
+        <v>1.818107210944952</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.127652413885954</v>
+        <v>2.150021986929517</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.489205468630779</v>
+        <v>2.53538630881102</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.953840662911247</v>
+        <v>3.025494846719646</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.749139504651055</v>
+        <v>2.821354399183555</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.018259441043938</v>
+        <v>3.114152764891941</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.879798728575601</v>
+        <v>3.000552792340315</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.152482735609638</v>
+        <v>3.3244814951763</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1985</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.473743919087809</v>
+        <v>1.467733089513821</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.978426843656223</v>
+        <v>1.977240057211567</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.986678128926378</v>
+        <v>1.986524738922057</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.865014103748997</v>
+        <v>1.864519611370994</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.175591049393852</v>
+        <v>1.224136969159623</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.271453744016348</v>
+        <v>1.295411152965961</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.244677893566298</v>
+        <v>2.292689572556618</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.583654589829941</v>
+        <v>2.632902152223657</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.724183768319762</v>
+        <v>2.797440878099458</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.284844317078061</v>
+        <v>3.384191642372635</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.878631823805271</v>
+        <v>2.978539859823947</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.416788313692081</v>
+        <v>3.540484934720325</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.047015294131825</v>
+        <v>3.195704841909652</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.071239609345767</v>
+        <v>3.243238368912429</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1834</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.990185387131952</v>
+        <v>1.96098959277932</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.178344986543586</v>
+        <v>2.17715820009893</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.729047974743835</v>
+        <v>1.728894584739514</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.859273118332197</v>
+        <v>1.858778625954194</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.484560446370629</v>
+        <v>1.533106366136401</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.400255086692745</v>
+        <v>1.424212495642358</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.678685403544357</v>
+        <v>2.726697082534677</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.811398657249434</v>
+        <v>2.860646219643151</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.132095890039636</v>
+        <v>3.205352999819333</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.64531776982755</v>
+        <v>3.744665095122123</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.440616611567357</v>
+        <v>3.540524647586032</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.020251034369792</v>
+        <v>4.143947655398037</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.654625808101095</v>
+        <v>3.803315355878922</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.716784577193501</v>
+        <v>3.888783336760163</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1681</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.18892335078629</v>
+        <v>2.159727556433658</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.600342849632035</v>
+        <v>2.59915606318738</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.908129466066761</v>
+        <v>1.90797607606244</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.276308208703313</v>
+        <v>2.27581371632531</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.916483854893762</v>
+        <v>1.965029774659534</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.035392685242705</v>
+        <v>2.059350094192318</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.021473521693373</v>
+        <v>3.069485200683694</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.030312076003007</v>
+        <v>3.079559638396724</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.504725517338642</v>
+        <v>3.577982627118338</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.082528315297907</v>
+        <v>4.18187564059248</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.996803956561799</v>
+        <v>4.096711992580474</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.447600907251449</v>
+        <v>4.571297528279693</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.205915253224177</v>
+        <v>4.354604801002004</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.312674103926625</v>
+        <v>4.484672863493287</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1513</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.914325212030086</v>
+        <v>1.885129417677454</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.352048570387282</v>
+        <v>2.350861783942626</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.758995625817306</v>
+        <v>1.758842235812985</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.690939209590724</v>
+        <v>1.690444717212721</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.549212776124911</v>
+        <v>1.597758695890683</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.582211392673415</v>
+        <v>1.606168801623028</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.422814979210287</v>
+        <v>2.470826658200608</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.277623400856456</v>
+        <v>3.326870963250173</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.877579777050144</v>
+        <v>3.95083688682984</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.613913459239782</v>
+        <v>4.713260784534356</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.078743034621354</v>
+        <v>4.178651070640029</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.707965866421496</v>
+        <v>4.831662487449741</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.353908866379726</v>
+        <v>4.502598414157553</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.183081396976384</v>
+        <v>4.355080156543046</v>
       </c>
     </row>
     <row r="26">
@@ -3257,98 +3257,98 @@
         <v>1306</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.730416281869942</v>
+        <v>1.701220487517311</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.722599254656025</v>
+        <v>2.721412468211369</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.098118834678935</v>
+        <v>2.097965444674614</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.228343978267297</v>
+        <v>2.227849485889294</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.766624103578962</v>
+        <v>1.815170023344734</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.523416203658144</v>
+        <v>2.547373612607757</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.434111663687538</v>
+        <v>3.482123342677859</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.728145623269867</v>
+        <v>4.777393185663584</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.126581537191193</v>
+        <v>5.199838646970889</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.272068560156896</v>
+        <v>5.371415885451469</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.837658366674653</v>
+        <v>4.937566402693328</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.484593946288776</v>
+        <v>5.60829056731702</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.064443092975367</v>
+        <v>5.213132640753194</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.290178743201899</v>
+        <v>5.462177502768562</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.8006</t>
+          <t>X &gt; 0.8005</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1108</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.843993716758064</v>
+        <v>2.814797922405432</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.857356360156331</v>
+        <v>2.856169573711675</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.823595805726207</v>
+        <v>2.823442415721885</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.675842609964384</v>
+        <v>3.675348117586381</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.776542226543775</v>
+        <v>2.825088146309547</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.712905425853961</v>
+        <v>2.736862834803574</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.711227557562516</v>
+        <v>3.759239236552837</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.410223895725231</v>
+        <v>5.459471458118948</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.800505277108599</v>
+        <v>5.873762386888295</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.943366264172248</v>
+        <v>6.042713589466821</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.738665105912055</v>
+        <v>5.838573141930731</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.134054088592279</v>
+        <v>6.257750709620524</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.894408650441328</v>
+        <v>6.043098198219155</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.390902423411546</v>
+        <v>6.562901182978209</v>
       </c>
     </row>
     <row r="28">
@@ -3358,205 +3358,205 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.665346157981354</v>
+        <v>2.576468261693101</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.979403835231722</v>
+        <v>3.915369098615173</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.042920641159242</v>
+        <v>2.980505569174923</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.389830508474581</v>
+        <v>3.326839826839823</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.634856231651909</v>
+        <v>2.621140469437684</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.932230261286996</v>
+        <v>2.893925988256612</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.714258796928739</v>
+        <v>3.699070764832022</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.522379752275256</v>
+        <v>5.505965277175953</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.894767043206436</v>
+        <v>5.901893100939581</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.019929503647973</v>
+        <v>6.052090494150576</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.706885983524288</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.499660668924037</v>
+        <v>6.55546743333003</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.296194539337606</v>
+        <v>6.376759723216416</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.521930189564138</v>
+        <v>6.625804585231784</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.8849</t>
+          <t>X &gt; 0.8848</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>744</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.164245259788224</v>
+        <v>3.135049465435593</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.838005403283546</v>
+        <v>3.83681861683889</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.964739394872595</v>
+        <v>1.964586004868274</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.170233355665253</v>
+        <v>3.16973886328725</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.631943802569559</v>
+        <v>2.680489722335331</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.601360842957334</v>
+        <v>3.625318251906947</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.457510698744926</v>
+        <v>4.505522377735247</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.200119474313027</v>
+        <v>5.249367036706744</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.407954522091323</v>
+        <v>5.48121163187102</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.170938951567919</v>
+        <v>6.270286276862493</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.369463599759335</v>
+        <v>6.46937163577801</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.747927773620034</v>
+        <v>7.871624394648279</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.462185522457162</v>
+        <v>7.610875070234989</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.687921172683694</v>
+        <v>7.859919932250357</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.927</t>
+          <t>X &gt; 0.9269</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>558</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.537005116419053</v>
+        <v>2.507809322066421</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.897145188229779</v>
+        <v>2.895958401785123</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.294488498815241</v>
+        <v>4.29433510881092</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.141559520539793</v>
+        <v>5.14106502816179</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.065635558841954</v>
+        <v>4.114181478607726</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.900643997079186</v>
+        <v>4.924601406028799</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.53277951594923</v>
+        <v>5.58079119493955</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.678614097968939</v>
+        <v>6.727861660362656</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.438420471912117</v>
+        <v>6.511677581691814</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.201404901388706</v>
+        <v>7.300752226683279</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.817492273594461</v>
+        <v>6.917400309613136</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.002408060358398</v>
+        <v>9.126104681386643</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.940680146113081</v>
+        <v>9.089369693890909</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>9.883261674475811</v>
+        <v>10.05526043404247</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.9692</t>
+          <t>X &gt; 0.9691</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.840071623786635</v>
+        <v>1.677080293339621</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.944934913438857</v>
+        <v>2.803262814095099</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.772385750906032</v>
+        <v>4.626273594253298</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.124833116716623</v>
+        <v>6.972906403940883</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.092716403127099</v>
+        <v>5.991046425550536</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.402436111774534</v>
+        <v>5.278610269492617</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.305380073496018</v>
+        <v>6.449481273863221</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>8.554360812425337</v>
+        <v>8.693008119391209</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.752637915161813</v>
+        <v>7.917119254096775</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.890373439819612</v>
+        <v>8.07851234815864</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.673326602547064</v>
+        <v>8.859593575499389</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.695359075890046</v>
+        <v>9.902981987741136</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.769035383070459</v>
+        <v>10.00043489861573</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.73551177403774</v>
+        <v>10.98839601678873</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>297</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.748040198421876</v>
+        <v>3.718844404069245</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.483655452159397</v>
+        <v>3.482468665714741</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.445786424306718</v>
+        <v>5.445633034302396</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.596213588097093</v>
+        <v>7.59571909571909</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.047823024900389</v>
+        <v>6.09636894466616</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.018597727936147</v>
+        <v>7.04255513688576</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.607288042070664</v>
+        <v>7.655299721060985</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.150320408384928</v>
+        <v>8.199567970778645</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.415937578461481</v>
+        <v>7.489194688241177</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.576119792232625</v>
+        <v>7.675467117527198</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>7.371418633972432</v>
+        <v>7.471326669991107</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.752598133129105</v>
+        <v>8.87629475415735</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.9150852869446</v>
+        <v>11.08708404651126</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>210</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.907897876401819</v>
+        <v>5.906711089957163</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.465507444027736</v>
+        <v>6.465354054023415</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.024304016187521</v>
+        <v>8.023809523809518</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.486014463091827</v>
+        <v>7.534560382857599</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.259578968917388</v>
+        <v>8.283536377867001</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.55582099060361</v>
+        <v>10.60383266959393</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.136371394435919</v>
+        <v>9.185618956829636</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.02777019029409</v>
+        <v>10.10102730007379</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.55880377491661</v>
+        <v>11.65815110021119</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.87791214046594</v>
+        <v>10.97782017648461</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.34086172139269</v>
+        <v>12.46455834242094</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.87309182046023</v>
+        <v>13.02178136823806</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>13.09882747068676</v>
+        <v>13.27082623025343</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>129</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.868512929759156</v>
+        <v>-2.897708724111787</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.047432760122753</v>
+        <v>4.046245973678097</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.303824166065382</v>
+        <v>8.303670776061061</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.658855511204131</v>
+        <v>7.658361018826128</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.446147353457285</v>
+        <v>9.494693273223056</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.51871518154198</v>
+        <v>10.54267259049159</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13.53478001607425</v>
+        <v>13.58279169506457</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.06771137228751</v>
+        <v>13.11695893468123</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.78192301421436</v>
+        <v>13.85518012399405</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.48239181478372</v>
+        <v>14.5817391400783</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.27769065652353</v>
+        <v>14.37759869254221</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.31206880887886</v>
+        <v>14.4357654299071</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.66711175401505</v>
+        <v>14.81580130179288</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>13.34245980734236</v>
+        <v>13.51445856690902</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3.471464921846604</v>
+        <v>3.442269127493972</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>14.95551692402087</v>
+        <v>14.95433013757621</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>20.51312649164678</v>
+        <v>20.51297310164246</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>17.07192306380657</v>
+        <v>17.07142857142857</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>20.10506208213945</v>
+        <v>20.15360800190522</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>15.64053134986976</v>
+        <v>15.66448875881937</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>15.55582099060359</v>
+        <v>15.60383266959391</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>15.08875234681685</v>
+        <v>15.13799990921057</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>15.02777019029408</v>
+        <v>15.10102730007377</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>15.36832758444042</v>
+        <v>15.467674909735</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>16.35410261665642</v>
+        <v>16.45401065267509</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>16.38848076901174</v>
+        <v>16.51217739003999</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>14.77785372522214</v>
+        <v>14.92654327299997</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.00358937544868</v>
+        <v>15.17558813501534</v>
       </c>
     </row>
   </sheetData>
@@ -3904,313 +3904,313 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.08461</t>
+          <t>X &lt; -0.08453</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.431707400211344</v>
+        <v>5.430520613766689</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.465507444027736</v>
+        <v>1.465354054023415</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.58125255832993</v>
+        <v>10.6297984780957</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7.307198016536439</v>
+        <v>7.331155425486052</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.603440038222658</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.136371394435919</v>
+        <v>9.185618956829636</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.503960666484559</v>
+        <v>5.577217776264256</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>4.753389195449273</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6983367509683305</v>
+        <v>-0.5496472031905029</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.908351280210582</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.04246</t>
+          <t>X &lt; -0.04238</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>120</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.185750636132312</v>
+        <v>4.15655484177968</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.907897876401826</v>
+        <v>0.9067110899571702</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.513126491646787</v>
+        <v>0.5129731016424657</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.310018301901806</v>
+        <v>2.309523809523803</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.438395415472776</v>
+        <v>8.486941335238548</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.23576944510787</v>
+        <v>1.259726854057483</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.151059085841695</v>
+        <v>6.199070764832015</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.350657108721627</v>
+        <v>7.399904671115344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.956341618865515</v>
+        <v>4.029598728645212</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.273089489202327</v>
+        <v>2.372436814496901</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.264945002391194</v>
+        <v>-1.165036966372519</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.230566850035871</v>
+        <v>-1.106870229007626</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.150717703349287</v>
+        <v>-4.002028155571459</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.424982053122747</v>
+        <v>-1.252983293556085</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003048</t>
+          <t>X &lt; -0.0002374</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>162</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>3.318109034008721</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.857534222363611</v>
+        <v>-2.559546578754492</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.017737705884088</v>
+        <v>-2.339787634553865</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.03566071044387087</v>
+        <v>0.2440841367221651</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.129753440164144</v>
+        <v>2.822319658346935</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.8938601845217562</v>
+        <v>-0.5858764179261584</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.490565258681208</v>
+        <v>1.807455222909724</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.875348466746324</v>
+        <v>3.182113260072398</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2720534428628767</v>
+        <v>0.07765598835892007</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.7298796126591114</v>
+        <v>1.094318205089948</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.178525249304776</v>
+        <v>-3.078617213286101</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.526863146332168</v>
+        <v>-2.403166525303924</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.798865851497439</v>
+        <v>-4.650176303719611</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.721278349419045</v>
+        <v>-2.549279589852382</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.04185</t>
+          <t>X &lt; 0.04191</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>240</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.519083969465655</v>
+        <v>2.676610166814264</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.4912312097351474</v>
+        <v>0.6784953223223127</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.013126491646773</v>
+        <v>2.774383890024197</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.060018301901813</v>
+        <v>1.244516893894485</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.188395415472776</v>
+        <v>2.000081030950859</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.652436111774534</v>
+        <v>1.857928790433689</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.98439241917503</v>
+        <v>2.212210460544327</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.600657108721627</v>
+        <v>3.821066496841489</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2063416188655225</v>
+        <v>0.4645918130158933</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.6064228225356558</v>
+        <v>0.885576510209205</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.59827833572453</v>
+        <v>-4.498370299705854</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.730566850035878</v>
+        <v>-3.606870229007633</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.150717703349287</v>
+        <v>-4.002028155571459</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.50831538645609</v>
+        <v>-3.336316626889428</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.084</t>
+          <t>X &lt; 0.08405</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>331</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.223011461912776</v>
+        <v>5.274319312837562</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.194906939845922</v>
+        <v>1.29593264684339</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.519168787719295</v>
+        <v>3.596805436971806</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.34727912768227</v>
+        <v>3.427288280581685</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.319563592713457</v>
+        <v>4.135643930048936</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.408478407847049</v>
+        <v>3.684651778982399</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.417423637704744</v>
+        <v>2.723094788856038</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.460929012044893</v>
+        <v>3.758763529974196</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.9830284265190912</v>
+        <v>1.319388518435005</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1331096301892316</v>
+        <v>0.3644046859828407</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.301198778826247</v>
+        <v>-4.201290742807572</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.360476215594787</v>
+        <v>-3.236779594566542</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.478512265282816</v>
+        <v>-3.329822717504989</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.950661811430912</v>
+        <v>-2.77866305186425</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.1261</t>
+          <t>X &lt; 0.1262</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>431</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.899594410300914</v>
+        <v>3.911906523736867</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.360334071297416</v>
+        <v>1.411298245920463</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.589692616936794</v>
+        <v>2.623064844761721</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.719917760525156</v>
+        <v>2.982306684141541</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.965850945248498</v>
+        <v>5.015993323006136</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.086890868155045</v>
+        <v>1.518347543712657</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.002180508888877</v>
+        <v>1.457691454487197</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9991489880719726</v>
+        <v>1.351517574341159</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.846055906269832</v>
+        <v>-1.557391263656555</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.927993264084606</v>
+        <v>-2.720155778095688</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.524805791254309</v>
+        <v>-4.424897755235634</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.562353392959317</v>
+        <v>-3.438656771931072</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.446541369242553</v>
+        <v>-4.297851821464725</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.756768596046193</v>
+        <v>-3.584769836479531</v>
       </c>
     </row>
     <row r="12">
@@ -4220,101 +4220,101 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.697655398037078</v>
+        <v>2.516343201568041</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1936121621161035</v>
+        <v>0.05133190124464448</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.298840777361065</v>
+        <v>2.126729715399073</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.357637349520857</v>
+        <v>1.374779541446202</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.140776367853739</v>
+        <v>3.178299359929916</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.7595789689173955</v>
+        <v>1.080103768073968</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6748686096512273</v>
+        <v>0.8427692336188244</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1493428912783656</v>
+        <v>0.2981347596109174</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.81746790494401</v>
+        <v>-1.4136636827023</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.203100986988147</v>
+        <v>-2.85254838384531</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.300659288105486</v>
+        <v>-4.029805649646541</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.730566850035878</v>
+        <v>-3.522199997278577</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.865003417634995</v>
+        <v>-4.630370401560768</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.460696338837039</v>
+        <v>-4.381325539545401</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.2104</t>
+          <t>X &lt; 0.2105</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>715</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.043559493941174</v>
+        <v>2.891550224974516</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.3134922819962256</v>
+        <v>0.2003398988214329</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.296343274863567</v>
+        <v>2.299676702750496</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.587407579291089</v>
+        <v>1.737039968341904</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.867299844377214</v>
+        <v>2.909840688885829</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.066771776110194</v>
+        <v>1.320984366771299</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1429005776831929</v>
+        <v>0.3657374314986939</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.3017643135856289</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.923611761087869</v>
+        <v>-1.655173787603623</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.633670417557575</v>
+        <v>-2.404411163187902</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.118091855538054</v>
+        <v>-2.952746463579231</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.664133283602311</v>
+        <v>-2.540436662574066</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.224144276775853</v>
+        <v>-3.075454728998025</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.138268766409475</v>
+        <v>-3.106130146702945</v>
       </c>
     </row>
     <row r="14">
@@ -4327,98 +4327,98 @@
         <v>853</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.501498975327308</v>
+        <v>2.426008964892347</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6558462937523402</v>
+        <v>0.6105438425704008</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.136807617086411</v>
+        <v>2.191254170167433</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.798099583652494</v>
+        <v>1.972706155632984</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.080443090345774</v>
+        <v>2.130352187951729</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7365510004029048</v>
+        <v>0.9560792017485937</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.05155912439666821</v>
+        <v>0.1442922100534645</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6358610624389769</v>
+        <v>-0.3743076976127711</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.165776395984032</v>
+        <v>-0.9314604613859458</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.015695192313892</v>
+        <v>-1.808849735210707</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.041029410363066</v>
+        <v>-2.88634844178236</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.654951375241033</v>
+        <v>-2.531254754212789</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.192335522810012</v>
+        <v>-3.043645975032184</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.732133284072347</v>
+        <v>-2.677367818761248</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.2947</t>
+          <t>X &lt; 0.2948</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.455545357539933</v>
+        <v>2.388045304113987</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.430869528405722</v>
+        <v>1.386827481809739</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.60012551412968</v>
+        <v>2.641974071574566</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.046088683133483</v>
+        <v>2.189898849937642</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.38756452593222</v>
+        <v>2.435161399963469</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.12091118508831</v>
+        <v>1.305888175729002</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.7429456938573367</v>
+        <v>0.9104845132107542</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5061366351688932</v>
+        <v>-0.2802316482614842</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3716153703817966</v>
+        <v>-0.1663077041033247</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.905796141296214</v>
+        <v>-1.716994079812039</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.697007563486025</v>
+        <v>-2.551755716372526</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.662629411130702</v>
+        <v>-2.538932790102457</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.278283685753983</v>
+        <v>-3.129594137976156</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.511087728269523</v>
+        <v>-2.489542433341043</v>
       </c>
     </row>
     <row r="16">
@@ -4428,101 +4428,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.55532779154143</v>
+        <v>1.537312541425365</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3560033129751332</v>
+        <v>0.3629662003414609</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7849551572151441</v>
+        <v>0.868655848985064</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2562017176074605</v>
+        <v>0.4261768484990043</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.118241653803366</v>
+        <v>1.209254483083619</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1800308399458643</v>
+        <v>0.3813484756791041</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3989134567173309</v>
+        <v>-0.2080330603045937</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7836097776045605</v>
+        <v>-0.5471831057509391</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9269642570268459</v>
+        <v>-0.7035704010756447</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.518233959452267</v>
+        <v>-2.304364061975299</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.887679763511464</v>
+        <v>-2.711089597951478</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.93567393405565</v>
+        <v>-2.773536895674297</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.064567662129171</v>
+        <v>-2.921781241991219</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.04214376929437</v>
+        <v>-3.001954486971727</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.379</t>
+          <t>X &lt; 0.3791</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2360917323449669</v>
+        <v>0.1916425610779342</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.8435145529767141</v>
+        <v>-0.9003064539024876</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.9558000620255385</v>
+        <v>-0.9431672492347332</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.178682263069938</v>
+        <v>-1.093984962406019</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1191863759247624</v>
+        <v>0.1395630580850025</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.289654283705687</v>
+        <v>-0.1814771749891335</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6893413853008212</v>
+        <v>-0.6258237499359183</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.15641002908756</v>
+        <v>-1.05364916421189</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.14672080751847</v>
+        <v>-1.05256089576794</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.420667872399562</v>
+        <v>-2.331580098822343</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.484026274476008</v>
+        <v>-2.356856430406374</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.058006736881701</v>
+        <v>-1.978429862035156</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.015190456357075</v>
+        <v>-1.982254144272019</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.458976387400369</v>
+        <v>-2.510045440448749</v>
       </c>
     </row>
     <row r="18">
@@ -4532,101 +4532,101 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.501029166926557</v>
+        <v>-0.4801305631755497</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.324806526113903</v>
+        <v>-1.376237067444464</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.216433256780896</v>
+        <v>-1.207826398669845</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.8975288679095144</v>
+        <v>-0.8571428571428612</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.07361554125894543</v>
+        <v>0.06292632585768843</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0565241620889978</v>
+        <v>0.1197602291096302</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3713868969567002</v>
+        <v>-0.282352737568317</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.775522878691838</v>
+        <v>-0.6514737749999426</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.8994376972662153</v>
+        <v>-0.7797011668615781</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.001087141802508</v>
+        <v>-1.88310479989039</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.513529017495046</v>
+        <v>-1.362777079366879</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.570617227869626</v>
+        <v>-1.45862902297749</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.515241962958612</v>
+        <v>-1.505170833132738</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.263569694989087</v>
+        <v>-2.324636341953322</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.4633</t>
+          <t>X &lt; 0.4634</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1745</v>
+        <v>1753</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1434017773986653</v>
+        <v>-0.1561696808143793</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.382461507511472</v>
+        <v>-1.399017781285039</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9786019738409593</v>
+        <v>-0.9419333078867496</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5324474515228559</v>
+        <v>-0.4978920058375209</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1574949954861253</v>
+        <v>-0.1615538379584933</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1144114039307809</v>
+        <v>-0.08497011563948575</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.6822742474916339</v>
+        <v>-0.6831539840783449</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.404345750054809</v>
+        <v>-1.402711938668496</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.350976848830314</v>
+        <v>-1.35220738025253</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.029369058539245</v>
+        <v>-2.031511553004997</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.859910677448411</v>
+        <v>-1.86304266437822</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.966113501438279</v>
+        <v>-2.001967150330323</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.954268677003348</v>
+        <v>-2.023990505828166</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.499480620457994</v>
+        <v>-2.630621627840178</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1892</v>
+        <v>1902</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.667989073098731</v>
+        <v>-0.6795678918325905</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.515866582062962</v>
+        <v>-1.53052740376669</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.279723140319568</v>
+        <v>-1.244349074089762</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7532817156328235</v>
+        <v>-0.7203035060177996</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3973050930315196</v>
+        <v>-0.3961302179900699</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.492300730330733</v>
+        <v>-0.4615059030579403</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.285749760919749</v>
+        <v>-1.279964874580976</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.777372396020205</v>
+        <v>-1.770257887877833</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.021078869625086</v>
+        <v>-2.041580005177799</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.68471641797067</v>
+        <v>-2.732550062143524</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.544628379699915</v>
+        <v>-2.593608394943956</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.64028173915942</v>
+        <v>-2.717485047714938</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.292556055171794</v>
+        <v>-2.401081783331712</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.830901714856374</v>
+        <v>-2.993256689980903</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2030</v>
+        <v>2041</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.060739732787042</v>
+        <v>-1.048123520793418</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.519833627762807</v>
+        <v>-1.510442906144206</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.620631470136658</v>
+        <v>-1.586003007572558</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.1213542471178</v>
+        <v>-1.088850174216027</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6036186437065609</v>
+        <v>-0.6248204998029294</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.623079099216632</v>
+        <v>-0.6185283542758526</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.712220246509794</v>
+        <v>-1.727569847446112</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.104156250806867</v>
+        <v>-2.118668153909098</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.433912271388373</v>
+        <v>-2.472031263204826</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.913734502931398</v>
+        <v>-2.976552096135848</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.698786615770445</v>
+        <v>-2.763176956583003</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.982535353972878</v>
+        <v>-3.070631247616838</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.83486344436357</v>
+        <v>-2.9498478517988</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.173750526029153</v>
+        <v>-3.337745664942673</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2175</v>
+        <v>2186</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.29261621334971</v>
+        <v>-1.28172237993703</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.645828689670424</v>
+        <v>-1.636510020142921</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.787879912744806</v>
+        <v>-1.77878839130247</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.633536236618404</v>
+        <v>-1.624902419984387</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.002996525919166</v>
+        <v>-1.042291770304352</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.047403558404113</v>
+        <v>-1.064034920479131</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.886673880855525</v>
+        <v>-1.921084273927661</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.237834408930823</v>
+        <v>-2.271628175599979</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.320416790920412</v>
+        <v>-2.375771726246008</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.824814748215452</v>
+        <v>-2.901535788242825</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.454109373373754</v>
+        <v>-2.533241626034474</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.946230607500276</v>
+        <v>-3.04471300780105</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.606600056290468</v>
+        <v>-2.72973734624361</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.677855616341141</v>
+        <v>-2.822059231342003</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2326</v>
+        <v>2337</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.518966479444138</v>
+        <v>-1.488835229142303</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.568577743786378</v>
+        <v>-1.560296147165019</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.341815741986089</v>
+        <v>-1.335408499720408</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.402881241477182</v>
+        <v>-1.39591575871934</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.10478802492694</v>
+        <v>-1.137952100396568</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9985921658604227</v>
+        <v>-1.012838888657512</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.960456845005567</v>
+        <v>-1.989211373962064</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.104745978756938</v>
+        <v>-2.133812785137323</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.31457215204825</v>
+        <v>-2.361662301813077</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.712604359152472</v>
+        <v>-2.778495835367835</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.550904641721388</v>
+        <v>-2.618028419363981</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.008917365499798</v>
+        <v>-3.092761635591643</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.718616285214353</v>
+        <v>-2.823670584998318</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.813632096115015</v>
+        <v>-2.936765920856047</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2479</v>
+        <v>2490</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.437577346746231</v>
+        <v>-1.411430242785507</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.623214126809742</v>
+        <v>-1.615271324111582</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.274022102730733</v>
+        <v>-1.268314383363538</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.484008750461932</v>
+        <v>-1.477142857142859</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.237381647764089</v>
+        <v>-1.26495942506557</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.280314189793621</v>
+        <v>-1.290980378395147</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.906731206461863</v>
+        <v>-1.93101867583011</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.950147720252211</v>
+        <v>-1.975095328884656</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.231259025256861</v>
+        <v>-2.271336475095609</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.616828620611081</v>
+        <v>-2.673005580584629</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.558256847677256</v>
+        <v>-2.615097134844241</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.864988454227735</v>
+        <v>-2.936725766728344</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.699104800123479</v>
+        <v>-2.788660030320557</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.81465530846765</v>
+        <v>-2.919649960222756</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2647</v>
+        <v>2658</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.052344601962929</v>
+        <v>-1.031264951056954</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.215080686967866</v>
+        <v>-1.209393778956695</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9880021765247733</v>
+        <v>-0.9838421849817465</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9129148307038903</v>
+        <v>-0.9088669950739003</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8286728576195941</v>
+        <v>-0.8531411544502348</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.8122531537621924</v>
+        <v>-0.8226687448422396</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.253487510490878</v>
+        <v>-1.275913600396251</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.775803501907845</v>
+        <v>-1.796792025581347</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.080611623970078</v>
+        <v>-2.114161441588855</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.495551275289067</v>
+        <v>-2.542414174734255</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.189473304277989</v>
+        <v>-2.237941889333811</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.549932648450373</v>
+        <v>-2.610629627503869</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.345581751687654</v>
+        <v>-2.421546771592517</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.288223458487316</v>
+        <v>-2.377889237875131</v>
       </c>
     </row>
     <row r="26">
@@ -4948,101 +4948,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2854</v>
+        <v>2865</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.7543726053512358</v>
+        <v>-0.738047891599976</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.126296122202504</v>
+        <v>-1.121443237467233</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9441160912502511</v>
+        <v>-0.9404344087886969</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9697768563849749</v>
+        <v>-0.9658385093167752</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7559228986499278</v>
+        <v>-0.7754107872388332</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.068563189413439</v>
+        <v>-1.075520854493398</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.449138980102617</v>
+        <v>-1.465738891621093</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.072419814355293</v>
+        <v>-2.087207833238537</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.219768909291176</v>
+        <v>-2.24508187530369</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.281377504033031</v>
+        <v>-2.318512412876174</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.082235866934425</v>
+        <v>-2.120406561909483</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.379026233789382</v>
+        <v>-2.427065555132501</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.184868316309007</v>
+        <v>-2.245224247685904</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.325472592716309</v>
+        <v>-2.396089750798673</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.8006</t>
+          <t>X &lt; 0.8005</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3052</v>
+        <v>3063</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9964135835523038</v>
+        <v>-0.9821534373707266</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9263057789506632</v>
+        <v>-0.9225572027257627</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.009890158696017</v>
+        <v>-1.006220131929439</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.286759403301765</v>
+        <v>-1.281972014318256</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.9583158989124954</v>
+        <v>-0.9726940814281164</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9047534307091283</v>
+        <v>-0.9103046232029115</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.233434757462213</v>
+        <v>-1.246640418664178</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.879231707498128</v>
+        <v>-1.890580829047572</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.988211864942137</v>
+        <v>-2.007993622506461</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.035374734183357</v>
+        <v>-2.064580900968814</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.960526017121147</v>
+        <v>-1.990216353195748</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.104830111332532</v>
+        <v>-2.142759299154449</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.01593224642167</v>
+        <v>-2.063385857921325</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.231010886674525</v>
+        <v>-2.286283979158441</v>
       </c>
     </row>
     <row r="28">
@@ -5052,205 +5052,205 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3237</v>
+        <v>3247</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.7270698766882049</v>
+        <v>-0.7002958739667378</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.029621360286392</v>
+        <v>-1.009520883040693</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.8538685822448429</v>
+        <v>-0.8344793231580354</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.9227093441304248</v>
+        <v>-0.9030439931575955</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7051658907502585</v>
+        <v>-0.7002003519031348</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.760892085451971</v>
+        <v>-0.7487216866491266</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.952311238860311</v>
+        <v>-0.9464936686856973</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.495318839474486</v>
+        <v>-1.488044913883122</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.570596485185476</v>
+        <v>-1.57003226766475</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.601743381310897</v>
+        <v>-1.608389597889037</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.511858582638119</v>
+        <v>-1.518883120218682</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.738439650282864</v>
+        <v>-1.751684017865742</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.678512638494439</v>
+        <v>-1.699072490546826</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.775615355563289</v>
+        <v>-1.802721513451381</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.8849</t>
+          <t>X &lt; 0.8848</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3416</v>
+        <v>3427</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6582271999715061</v>
+        <v>-0.6496467086079107</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.737376335966907</v>
+        <v>-0.7347544523516518</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.4162578094912419</v>
+        <v>-0.4148919361702212</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6497014879405754</v>
+        <v>-0.6475123654349773</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5299744142109191</v>
+        <v>-0.5390578886652051</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7132180938329498</v>
+        <v>-0.7162556786936136</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.8698290240034652</v>
+        <v>-0.8777104427004971</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.058168139671118</v>
+        <v>-1.065723059732314</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.074107567532224</v>
+        <v>-1.086951387904911</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.235682440622234</v>
+        <v>-1.25381403559539</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.278106745590968</v>
+        <v>-1.296232301649489</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.578723666887839</v>
+        <v>-1.601183439856278</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.514633418889233</v>
+        <v>-1.542868295594801</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.594771280289031</v>
+        <v>-1.627946818505023</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.927</t>
+          <t>X &lt; 0.9269</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3602</v>
+        <v>3613</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3647334579202379</v>
+        <v>-0.3589811023276894</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3566289636645905</v>
+        <v>-0.355357875560081</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6534940453031197</v>
+        <v>-0.6514860595054515</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.757534300534509</v>
+        <v>-0.7551555538030925</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5886515705883255</v>
+        <v>-0.5945974094697135</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6917467137102307</v>
+        <v>-0.6934628725373813</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.7615205761145276</v>
+        <v>-0.7668592535841867</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9641987671098562</v>
+        <v>-0.9691199213135064</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.899263223570486</v>
+        <v>-0.9082122166284208</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.013100194657909</v>
+        <v>-1.025867489253905</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.9528784281886971</v>
+        <v>-0.9659219221247355</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.291610135274503</v>
+        <v>-1.30742347935341</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.280193140485011</v>
+        <v>-1.300035903219495</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.455520642795165</v>
+        <v>-1.478557608529798</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.9692</t>
+          <t>X &lt; 0.9691</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3755</v>
+        <v>3765</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1719988330821209</v>
+        <v>-0.1543680451093223</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2296120784694295</v>
+        <v>-0.2145491695080182</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5038676666113133</v>
+        <v>-0.4880862203914376</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.731150356796725</v>
+        <v>-0.7147587511826003</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6175734120157017</v>
+        <v>-0.6068583467964288</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.5183717542897739</v>
+        <v>-0.5052258802830067</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5887069960296429</v>
+        <v>-0.6045700976635615</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.855272165407591</v>
+        <v>-0.8704480204783991</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.7422399414181697</v>
+        <v>-0.7604101130877723</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.7529812742986053</v>
+        <v>-0.7738442503302068</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.8365256303848128</v>
+        <v>-0.8571813400455639</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.947095995630761</v>
+        <v>-0.9701566638364056</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.9531671176197847</v>
+        <v>-0.9789267216893549</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.085434782816499</v>
+        <v>-1.113541062480394</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3863</v>
+        <v>3874</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2621337807923538</v>
+        <v>-0.2590184366698551</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1824247042433385</v>
+        <v>-0.1818118127705688</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4084016446464531</v>
+        <v>-0.4072328185634646</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5482311171531862</v>
+        <v>-0.5466382227453366</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4269627112489758</v>
+        <v>-0.4297038703584874</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4771815580782146</v>
+        <v>-0.4777795859219154</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4962277358637266</v>
+        <v>-0.4987304891403213</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5615941189857949</v>
+        <v>-0.5640128546578538</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4791978502830574</v>
+        <v>-0.4838067882405781</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4874483954627848</v>
+        <v>-0.4941610882020839</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4708425709375064</v>
+        <v>-0.4776498113557608</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5772680143308335</v>
+        <v>-0.5857143982542752</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.672456833784068</v>
+        <v>-0.6826733168617807</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7687563218258404</v>
+        <v>-0.7806033245318247</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3950</v>
+        <v>3961</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.09635887686288669</v>
+        <v>-0.09440976147480029</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2304161064351362</v>
+        <v>-0.2297097507173902</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.333881839582709</v>
+        <v>-0.3329483485086016</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3920019001184016</v>
+        <v>-0.39088750584596</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3609646922985377</v>
+        <v>-0.3627647940645531</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.378261210105201</v>
+        <v>-0.3785951414073736</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4745411163316575</v>
+        <v>-0.4759964394690499</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4223459246454055</v>
+        <v>-0.4240176883502542</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4442062108858451</v>
+        <v>-0.4472040953588206</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5215488517182578</v>
+        <v>-0.5258397723042805</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4845250681640323</v>
+        <v>-0.4889522035067273</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5625506557038946</v>
+        <v>-0.5681369461411165</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.5889611860119075</v>
+        <v>-0.5959201293220886</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.6275136986923755</v>
+        <v>-0.6357149269819899</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4031</v>
+        <v>4042</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1155231386051128</v>
+        <v>0.1162753514385457</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04807541076117872</v>
+        <v>-0.04790163821254367</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.256294587027142</v>
+        <v>-0.2555933923126403</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2116347542724029</v>
+        <v>-0.2110421661260773</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2662250465734175</v>
+        <v>-0.2672757305065332</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2771875574505245</v>
+        <v>-0.277310182979555</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.348445619457955</v>
+        <v>-0.349253924391661</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3561796512486453</v>
+        <v>-0.3570123249320929</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.354031688039008</v>
+        <v>-0.3557484420985446</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.3725115021235723</v>
+        <v>-0.375132801584833</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3650937381373609</v>
+        <v>-0.3677563730474347</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3664458483002022</v>
+        <v>-0.3699760648137698</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3759161160476907</v>
+        <v>-0.3803363425613142</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3594896194834547</v>
+        <v>-0.3648091223537122</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4076</v>
+        <v>4087</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.04755824134383602</v>
+        <v>-0.0466971907406375</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2271314778056137</v>
+        <v>-0.2264921303404748</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4129806774258924</v>
+        <v>-0.4118682843995103</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3184692164535505</v>
+        <v>-0.3176017294884801</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3784140500514965</v>
+        <v>-0.3786185605947807</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2635776002724839</v>
+        <v>-0.2634721691415436</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2370134098722332</v>
+        <v>-0.2375845030396562</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2497838515919426</v>
+        <v>-0.2503518644331493</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2238021367499314</v>
+        <v>-0.2250444776109006</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2269105107976728</v>
+        <v>-0.2288016764996001</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2463129847398164</v>
+        <v>-0.2481665507246049</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2472416906440174</v>
+        <v>-0.2496924349259544</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2121599402882168</v>
+        <v>-0.215335396275961</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.242450159109012</v>
+        <v>-0.2461323026091833</v>
       </c>
     </row>
   </sheetData>
